--- a/MyFunctional Testing Reports - AirBNB (1).xlsx
+++ b/MyFunctional Testing Reports - AirBNB (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2492279_cognizant_com/Documents/Microsoft Teams Chat Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2492262_cognizant_com/Documents/Desktop/HireGrad-SDET-final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1865" documentId="13_ncr:1_{9B4D69C6-458A-42F1-A3F1-7E73496B7B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C7EEB48-7060-440F-8D66-B305F5331AFE}"/>
+  <xr:revisionPtr revIDLastSave="1878" documentId="13_ncr:1_{9B4D69C6-458A-42F1-A3F1-7E73496B7B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7432A0EC-7EA4-4DF9-BBD2-8D13A3B4D720}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="5" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2356" uniqueCount="837">
   <si>
     <t>Note</t>
   </si>
@@ -1323,9 +1323,6 @@
     <t>DF07</t>
   </si>
   <si>
-    <t>There is no option to delete any application so once data populated it can't be removed then</t>
-  </si>
-  <si>
     <t>TC27</t>
   </si>
   <si>
@@ -1578,9 +1575,6 @@
     <t xml:space="preserve">"Cognizant" company applicants were displayed but along with that other applicants who are not yet selected are also displayed </t>
   </si>
   <si>
-    <t>DF08</t>
-  </si>
-  <si>
     <t xml:space="preserve">The selected company applicants were displayed but along with that other applicants who are not yet selected in any company are also displayed </t>
   </si>
   <si>
@@ -1603,12 +1597,6 @@
   </si>
   <si>
     <t>Company and student data is visible as usual</t>
-  </si>
-  <si>
-    <t>DF09</t>
-  </si>
-  <si>
-    <t>There is no option to delete any job posting or company details so once data populated it can't be removed then</t>
   </si>
   <si>
     <t>TC36</t>
@@ -2700,27 +2688,10 @@
     <t>7</t>
   </si>
   <si>
-    <t>No option to delete application in Application Management page</t>
-  </si>
-  <si>
-    <t>Step 1: Load the HireGrad application in Chrome browser.
-Step 2: Login with valid Admin credentials.
-Step 3: Navigate to Application Management page /admin/applications.
-Step 4: Verify applicants data is already available.
-Step 5: Try to delete/remove application details to validate no application state.
-Expected Result:
-Admin should be able to delete/remove application details or system should display No Applications Available message when no application exists.
-Actual Result:
-There is no option to delete any application so once data populated it can't be removed. Applicants details are visible as usual.</t>
-  </si>
-  <si>
     <t>Mihir</t>
   </si>
   <si>
     <t>26-06-2026</t>
-  </si>
-  <si>
-    <t>8</t>
   </si>
   <si>
     <t>Company-wise placement details shows unselected applicants also</t>
@@ -2740,26 +2711,6 @@
     <t>The selected company applicants were displayed but along with that other applicants who are not yet selected in any company are also displayed</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>No option to delete job posting or applicant details to verify empty placement report</t>
-  </si>
-  <si>
-    <t>Step 1: Load the HireGrad application in Chrome browser.
-Step 2: Login with valid Admin credentials.
-Step 3: Navigate to Reports page /admin/reports.
-Step 4: Try to delete/remove job posting or applicant details to validate no placement data state.
-Step 5: Observe the placement report content.
-Expected Result:
-Admin should be able to delete/remove job posting or applicant details and Reports page should show No Data Available when no placement data exists.
-Actual Result:
-There is no option to delete any job posting or applicant details so once data populated it can't be removed. Company and student data is visible as usual.</t>
-  </si>
-  <si>
-    <t>There is no option to delete any job posting or applicant details so once data populated it can't be removed then</t>
-  </si>
-  <si>
     <t>Serial no</t>
   </si>
   <si>
@@ -2827,6 +2778,12 @@
   </si>
   <si>
     <t>Theme, Logout, and Protected Navigation</t>
+  </si>
+  <si>
+    <t>TS21, TS22, TS23, TS24, TS25, TS26</t>
+  </si>
+  <si>
+    <t>TS27, TS28, TS29, TS30, TS31, TS32, TS33, TS34, TS35</t>
   </si>
 </sst>
 </file>
@@ -3407,7 +3364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="3"/>
@@ -3771,13 +3728,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="27.453125" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" customWidth="1"/>
-    <col min="4" max="4" width="59.5703125" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" customWidth="1"/>
+    <col min="4" max="4" width="59.54296875" customWidth="1"/>
+    <col min="5" max="5" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3831,7 +3788,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="29.1">
+    <row r="4" spans="1:5" ht="29">
       <c r="A4" s="7" t="s">
         <v>20</v>
       </c>
@@ -3848,7 +3805,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="24.95" customHeight="1">
+    <row r="5" spans="1:5" ht="25" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>20</v>
       </c>
@@ -3865,7 +3822,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="29.1">
+    <row r="6" spans="1:5" ht="29">
       <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
@@ -3882,7 +3839,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="29.1">
+    <row r="7" spans="1:5" ht="29">
       <c r="A7" s="7" t="s">
         <v>20</v>
       </c>
@@ -3931,7 +3888,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="4" customFormat="1" ht="72.599999999999994">
+    <row r="10" spans="1:5" s="4" customFormat="1" ht="72.5">
       <c r="A10" s="8" t="s">
         <v>38</v>
       </c>
@@ -3948,7 +3905,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="29.1">
+    <row r="11" spans="1:5" ht="29">
       <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
@@ -3965,7 +3922,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="29.1">
+    <row r="12" spans="1:5" ht="29">
       <c r="A12" s="7" t="s">
         <v>38</v>
       </c>
@@ -3982,7 +3939,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="29.1">
+    <row r="13" spans="1:5" ht="29">
       <c r="A13" s="7" t="s">
         <v>38</v>
       </c>
@@ -4059,23 +4016,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K332"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="39.5703125" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" customWidth="1"/>
-    <col min="6" max="6" width="55.85546875" customWidth="1"/>
-    <col min="7" max="7" width="45.42578125" customWidth="1"/>
-    <col min="8" max="8" width="37.85546875" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.54296875" customWidth="1"/>
+    <col min="5" max="5" width="24.26953125" customWidth="1"/>
+    <col min="6" max="6" width="55.81640625" customWidth="1"/>
+    <col min="7" max="7" width="45.453125" customWidth="1"/>
+    <col min="8" max="8" width="37.81640625" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="12.26953125" customWidth="1"/>
+    <col min="12" max="12" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="15">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="23" t="s">
         <v>62</v>
       </c>
@@ -4110,7 +4067,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="30.75">
+    <row r="2" spans="1:11" ht="29">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -4141,7 +4098,7 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:11" ht="15">
+    <row r="3" spans="1:11">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -4162,7 +4119,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:11" ht="30.75">
+    <row r="4" spans="1:11">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -4183,7 +4140,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="30.75">
+    <row r="5" spans="1:11" ht="29">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -4204,7 +4161,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="30.75">
+    <row r="6" spans="1:11" ht="29">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -4225,7 +4182,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="1:11" ht="30.75">
+    <row r="7" spans="1:11" ht="29">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -4256,7 +4213,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="1:11" ht="15">
+    <row r="8" spans="1:11">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -4277,7 +4234,7 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="1:11" ht="30.75">
+    <row r="9" spans="1:11">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -4298,7 +4255,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="1:11" ht="30.75">
+    <row r="10" spans="1:11" ht="29">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -4319,7 +4276,7 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="1:11" ht="30.75">
+    <row r="11" spans="1:11" ht="29">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -4340,7 +4297,7 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:11" ht="30.75">
+    <row r="12" spans="1:11" ht="29">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -4371,7 +4328,7 @@
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="1:11" ht="15">
+    <row r="13" spans="1:11">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -4392,7 +4349,7 @@
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:11" ht="30.75">
+    <row r="14" spans="1:11">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -4413,7 +4370,7 @@
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
     </row>
-    <row r="15" spans="1:11" ht="30.75">
+    <row r="15" spans="1:11" ht="29">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -4434,7 +4391,7 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="1:11" ht="30.75">
+    <row r="16" spans="1:11" ht="29">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -4455,7 +4412,7 @@
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
     </row>
-    <row r="17" spans="1:11" ht="30.75">
+    <row r="17" spans="1:11" ht="29">
       <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
@@ -4486,7 +4443,7 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:11" ht="15">
+    <row r="18" spans="1:11">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -4507,7 +4464,7 @@
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
     </row>
-    <row r="19" spans="1:11" ht="30.75">
+    <row r="19" spans="1:11">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -4528,7 +4485,7 @@
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
     </row>
-    <row r="20" spans="1:11" ht="45.75">
+    <row r="20" spans="1:11" ht="43.5">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -4549,7 +4506,7 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="1:11" ht="30.75">
+    <row r="21" spans="1:11" ht="29">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
@@ -4580,7 +4537,7 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="1:11" ht="15">
+    <row r="22" spans="1:11">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -4601,7 +4558,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="1:11" ht="30.75">
+    <row r="23" spans="1:11" ht="29">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -4622,7 +4579,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="1:11" ht="30.75">
+    <row r="24" spans="1:11" ht="29">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -4643,7 +4600,7 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:11" ht="30.75">
+    <row r="25" spans="1:11" ht="29">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -4664,7 +4621,7 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="1:11" ht="30.75">
+    <row r="26" spans="1:11" ht="29">
       <c r="A26" s="4" t="s">
         <v>16</v>
       </c>
@@ -4695,7 +4652,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:11" ht="15">
+    <row r="27" spans="1:11">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -4716,7 +4673,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:11" ht="30.75">
+    <row r="28" spans="1:11" ht="29">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -4737,7 +4694,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:11" ht="30.75">
+    <row r="29" spans="1:11" ht="29">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -4758,7 +4715,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" spans="1:11" ht="30.75">
+    <row r="30" spans="1:11" ht="29">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -4779,7 +4736,7 @@
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
     </row>
-    <row r="31" spans="1:11" ht="30.75">
+    <row r="31" spans="1:11" ht="29">
       <c r="A31" s="4" t="s">
         <v>16</v>
       </c>
@@ -4810,7 +4767,7 @@
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
     </row>
-    <row r="32" spans="1:11" ht="15">
+    <row r="32" spans="1:11">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -4831,7 +4788,7 @@
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
     </row>
-    <row r="33" spans="1:11" ht="30.75">
+    <row r="33" spans="1:11" ht="29">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -4852,7 +4809,7 @@
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
     </row>
-    <row r="34" spans="1:11" ht="30.75">
+    <row r="34" spans="1:11" ht="29">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -4873,7 +4830,7 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="1:11" ht="30.75">
+    <row r="35" spans="1:11" ht="29">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -4894,7 +4851,7 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="1:11" ht="45.75">
+    <row r="36" spans="1:11" ht="29">
       <c r="A36" s="4" t="s">
         <v>16</v>
       </c>
@@ -4925,7 +4882,7 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="37" spans="1:11" ht="15">
+    <row r="37" spans="1:11">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -4946,7 +4903,7 @@
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
     </row>
-    <row r="38" spans="1:11" ht="30.75">
+    <row r="38" spans="1:11" ht="29">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -4967,7 +4924,7 @@
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
     </row>
-    <row r="39" spans="1:11" ht="45.75">
+    <row r="39" spans="1:11" ht="43.5">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -4988,7 +4945,7 @@
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
     </row>
-    <row r="40" spans="1:11" ht="30.75">
+    <row r="40" spans="1:11" ht="29">
       <c r="A40" s="4" t="s">
         <v>16</v>
       </c>
@@ -5019,7 +4976,7 @@
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
     </row>
-    <row r="41" spans="1:11" ht="15">
+    <row r="41" spans="1:11">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -5040,7 +4997,7 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
     </row>
-    <row r="42" spans="1:11" ht="30.75">
+    <row r="42" spans="1:11" ht="29">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -5061,7 +5018,7 @@
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
     </row>
-    <row r="43" spans="1:11" ht="30.75">
+    <row r="43" spans="1:11" ht="29">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -5082,7 +5039,7 @@
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
     </row>
-    <row r="44" spans="1:11" ht="30.75">
+    <row r="44" spans="1:11" ht="29">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -5103,7 +5060,7 @@
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
     </row>
-    <row r="45" spans="1:11" ht="45.75">
+    <row r="45" spans="1:11" ht="43.5">
       <c r="A45" s="4" t="s">
         <v>16</v>
       </c>
@@ -5134,7 +5091,7 @@
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" spans="1:11" ht="30.75">
+    <row r="46" spans="1:11" ht="29">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -5155,7 +5112,7 @@
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
     </row>
-    <row r="47" spans="1:11" ht="121.5">
+    <row r="47" spans="1:11" ht="87">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -5180,7 +5137,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="45.75">
+    <row r="48" spans="1:11" ht="43.5">
       <c r="A48" s="4" t="s">
         <v>16</v>
       </c>
@@ -5211,7 +5168,7 @@
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
     </row>
-    <row r="49" spans="1:11" ht="30.75">
+    <row r="49" spans="1:11" ht="29">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -5232,7 +5189,7 @@
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
     </row>
-    <row r="50" spans="1:11" ht="30.75">
+    <row r="50" spans="1:11" ht="29">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -5253,7 +5210,7 @@
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
     </row>
-    <row r="51" spans="1:11" ht="30.75">
+    <row r="51" spans="1:11" ht="29">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -5274,7 +5231,7 @@
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
     </row>
-    <row r="52" spans="1:11" ht="45.75">
+    <row r="52" spans="1:11" ht="43.5">
       <c r="A52" s="4" t="s">
         <v>16</v>
       </c>
@@ -5305,7 +5262,7 @@
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
     </row>
-    <row r="53" spans="1:11" ht="30.75">
+    <row r="53" spans="1:11" ht="29">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -5326,7 +5283,7 @@
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
     </row>
-    <row r="54" spans="1:11" ht="30.75">
+    <row r="54" spans="1:11" ht="29">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -5347,7 +5304,7 @@
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
     </row>
-    <row r="55" spans="1:11" ht="30.75">
+    <row r="55" spans="1:11" ht="29">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -5368,7 +5325,7 @@
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
     </row>
-    <row r="56" spans="1:11" ht="30.75">
+    <row r="56" spans="1:11" ht="29">
       <c r="A56" s="4" t="s">
         <v>16</v>
       </c>
@@ -5399,7 +5356,7 @@
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
     </row>
-    <row r="57" spans="1:11" ht="30.75">
+    <row r="57" spans="1:11" ht="29">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -5441,7 +5398,7 @@
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
     </row>
-    <row r="59" spans="1:11" ht="30.75">
+    <row r="59" spans="1:11" ht="29">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -5462,7 +5419,7 @@
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
     </row>
-    <row r="60" spans="1:11" ht="30.75">
+    <row r="60" spans="1:11" ht="29">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -5479,7 +5436,7 @@
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
     </row>
-    <row r="61" spans="1:11" ht="45.75">
+    <row r="61" spans="1:11" ht="43.5">
       <c r="A61" s="8" t="s">
         <v>21</v>
       </c>
@@ -5510,7 +5467,7 @@
       <c r="J61" s="4"/>
       <c r="K61" s="4"/>
     </row>
-    <row r="62" spans="1:11" ht="106.5">
+    <row r="62" spans="1:11" ht="101.5">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -5531,7 +5488,7 @@
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
     </row>
-    <row r="63" spans="1:11" ht="60.75">
+    <row r="63" spans="1:11" ht="58">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -5552,7 +5509,7 @@
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
     </row>
-    <row r="64" spans="1:11" ht="30.75">
+    <row r="64" spans="1:11" ht="29">
       <c r="A64" s="8" t="s">
         <v>21</v>
       </c>
@@ -5583,7 +5540,7 @@
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
     </row>
-    <row r="65" spans="1:11" ht="30.75">
+    <row r="65" spans="1:11" ht="29">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -5604,7 +5561,7 @@
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
     </row>
-    <row r="66" spans="1:11" ht="30.75">
+    <row r="66" spans="1:11" ht="29">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -5625,7 +5582,7 @@
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
     </row>
-    <row r="67" spans="1:11" ht="30.75">
+    <row r="67" spans="1:11" ht="29">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -5646,7 +5603,7 @@
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
     </row>
-    <row r="68" spans="1:11" ht="30.75">
+    <row r="68" spans="1:11" ht="29">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -5667,7 +5624,7 @@
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
     </row>
-    <row r="69" spans="1:11" ht="30.75">
+    <row r="69" spans="1:11" ht="29">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -5688,7 +5645,7 @@
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
     </row>
-    <row r="70" spans="1:11" ht="30.75">
+    <row r="70" spans="1:11" ht="29">
       <c r="A70" s="8" t="s">
         <v>21</v>
       </c>
@@ -5719,7 +5676,7 @@
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
     </row>
-    <row r="71" spans="1:11" ht="91.5">
+    <row r="71" spans="1:11" ht="87">
       <c r="A71" s="8"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -5740,7 +5697,7 @@
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
     </row>
-    <row r="72" spans="1:11" ht="45.75">
+    <row r="72" spans="1:11" ht="43.5">
       <c r="A72" s="8"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -5761,7 +5718,7 @@
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
     </row>
-    <row r="73" spans="1:11" ht="45.75">
+    <row r="73" spans="1:11" ht="43.5">
       <c r="A73" s="8" t="s">
         <v>23</v>
       </c>
@@ -5792,7 +5749,7 @@
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
     </row>
-    <row r="74" spans="1:11" ht="30.75">
+    <row r="74" spans="1:11" ht="29">
       <c r="A74" s="8"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -5813,7 +5770,7 @@
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
     </row>
-    <row r="75" spans="1:11" ht="30.75">
+    <row r="75" spans="1:11">
       <c r="A75" s="8"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -5834,7 +5791,7 @@
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
     </row>
-    <row r="76" spans="1:11" ht="106.5">
+    <row r="76" spans="1:11" ht="101.5">
       <c r="A76" s="8"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -5855,7 +5812,7 @@
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
     </row>
-    <row r="77" spans="1:11" ht="60.75">
+    <row r="77" spans="1:11" ht="58">
       <c r="A77" s="8" t="s">
         <v>23</v>
       </c>
@@ -5890,7 +5847,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="60.75">
+    <row r="78" spans="1:11" ht="58">
       <c r="A78" s="8"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -5917,7 +5874,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="60.75">
+    <row r="79" spans="1:11" ht="58">
       <c r="A79" s="8"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -5944,7 +5901,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="15">
+    <row r="80" spans="1:11">
       <c r="A80" s="8"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5967,7 +5924,7 @@
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
     </row>
-    <row r="81" spans="1:11" ht="30.75">
+    <row r="81" spans="1:11" ht="29">
       <c r="A81" s="8"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
@@ -5990,7 +5947,7 @@
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
     </row>
-    <row r="82" spans="1:11" ht="15">
+    <row r="82" spans="1:11">
       <c r="A82" s="8"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -6013,7 +5970,7 @@
       <c r="J82" s="4"/>
       <c r="K82" s="4"/>
     </row>
-    <row r="83" spans="1:11" ht="15">
+    <row r="83" spans="1:11">
       <c r="A83" s="8"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
@@ -6036,7 +5993,7 @@
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
     </row>
-    <row r="84" spans="1:11" ht="60.75">
+    <row r="84" spans="1:11" ht="58">
       <c r="A84" s="8"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -6063,7 +6020,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="30.75">
+    <row r="85" spans="1:11" ht="29">
       <c r="A85" s="8"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
@@ -6086,7 +6043,7 @@
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
     </row>
-    <row r="86" spans="1:11" ht="15">
+    <row r="86" spans="1:11">
       <c r="A86" s="8"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -6107,7 +6064,7 @@
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
     </row>
-    <row r="87" spans="1:11" ht="30.6" customHeight="1">
+    <row r="87" spans="1:11" ht="30.65" customHeight="1">
       <c r="A87" s="8"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
@@ -6132,7 +6089,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="45.75">
+    <row r="88" spans="1:11" ht="29">
       <c r="A88" s="8" t="s">
         <v>23</v>
       </c>
@@ -6161,7 +6118,7 @@
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
     </row>
-    <row r="89" spans="1:11" ht="30.75">
+    <row r="89" spans="1:11" ht="29">
       <c r="A89" s="8"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
@@ -6182,7 +6139,7 @@
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
     </row>
-    <row r="90" spans="1:11" ht="30.75">
+    <row r="90" spans="1:11" ht="29">
       <c r="A90" s="8"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -6203,7 +6160,7 @@
       <c r="J90" s="4"/>
       <c r="K90" s="4"/>
     </row>
-    <row r="91" spans="1:11" ht="30.75">
+    <row r="91" spans="1:11" ht="29">
       <c r="A91" s="8" t="s">
         <v>23</v>
       </c>
@@ -6232,7 +6189,7 @@
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
     </row>
-    <row r="92" spans="1:11" ht="30.75">
+    <row r="92" spans="1:11" ht="29">
       <c r="A92" s="8"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
@@ -6253,7 +6210,7 @@
       <c r="J92" s="4"/>
       <c r="K92" s="4"/>
     </row>
-    <row r="93" spans="1:11" ht="30.75">
+    <row r="93" spans="1:11" ht="29">
       <c r="A93" s="8"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
@@ -6274,7 +6231,7 @@
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
     </row>
-    <row r="94" spans="1:11" ht="30.75">
+    <row r="94" spans="1:11" ht="29">
       <c r="A94" s="8"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
@@ -6295,7 +6252,7 @@
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
     </row>
-    <row r="95" spans="1:11" ht="30.75">
+    <row r="95" spans="1:11" ht="29">
       <c r="A95" s="8"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
@@ -6316,7 +6273,7 @@
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
     </row>
-    <row r="96" spans="1:11" ht="30.75">
+    <row r="96" spans="1:11">
       <c r="A96" s="21" t="s">
         <v>26</v>
       </c>
@@ -6345,7 +6302,7 @@
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
     </row>
-    <row r="97" spans="1:11" ht="15">
+    <row r="97" spans="1:11">
       <c r="A97" s="21" t="s">
         <v>314</v>
       </c>
@@ -6374,7 +6331,7 @@
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
     </row>
-    <row r="98" spans="1:11" ht="30.75">
+    <row r="98" spans="1:11">
       <c r="A98" s="21" t="s">
         <v>314</v>
       </c>
@@ -6403,7 +6360,7 @@
       <c r="J98" s="4"/>
       <c r="K98" s="4"/>
     </row>
-    <row r="99" spans="1:11" ht="30.75">
+    <row r="99" spans="1:11" ht="29">
       <c r="A99" s="21" t="s">
         <v>314</v>
       </c>
@@ -6434,7 +6391,7 @@
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
     </row>
-    <row r="100" spans="1:11" ht="30.75">
+    <row r="100" spans="1:11" ht="29">
       <c r="A100" s="21" t="s">
         <v>314</v>
       </c>
@@ -6463,7 +6420,7 @@
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
     </row>
-    <row r="101" spans="1:11" ht="30.75">
+    <row r="101" spans="1:11" ht="29">
       <c r="A101" s="21" t="s">
         <v>314</v>
       </c>
@@ -6492,7 +6449,7 @@
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
     </row>
-    <row r="102" spans="1:11" ht="76.5">
+    <row r="102" spans="1:11" ht="72.5">
       <c r="A102" s="21" t="s">
         <v>314</v>
       </c>
@@ -6521,7 +6478,7 @@
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
     </row>
-    <row r="103" spans="1:11" ht="30.75">
+    <row r="103" spans="1:11" ht="29">
       <c r="A103" s="21" t="s">
         <v>26</v>
       </c>
@@ -6550,7 +6507,7 @@
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
     </row>
-    <row r="104" spans="1:11" ht="30.75">
+    <row r="104" spans="1:11" ht="29">
       <c r="A104" s="21" t="s">
         <v>314</v>
       </c>
@@ -6579,7 +6536,7 @@
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
     </row>
-    <row r="105" spans="1:11" ht="30.75">
+    <row r="105" spans="1:11">
       <c r="A105" s="21" t="s">
         <v>314</v>
       </c>
@@ -6608,7 +6565,7 @@
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
     </row>
-    <row r="106" spans="1:11" ht="30.75">
+    <row r="106" spans="1:11" ht="29">
       <c r="A106" s="21" t="s">
         <v>314</v>
       </c>
@@ -6639,7 +6596,7 @@
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
     </row>
-    <row r="107" spans="1:11" ht="30.75">
+    <row r="107" spans="1:11" ht="29">
       <c r="A107" s="21" t="s">
         <v>314</v>
       </c>
@@ -6668,7 +6625,7 @@
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
     </row>
-    <row r="108" spans="1:11" ht="30.75">
+    <row r="108" spans="1:11" ht="29">
       <c r="A108" s="21" t="s">
         <v>314</v>
       </c>
@@ -6697,7 +6654,7 @@
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
     </row>
-    <row r="109" spans="1:11" ht="30.75">
+    <row r="109" spans="1:11" ht="29">
       <c r="A109" s="21" t="s">
         <v>314</v>
       </c>
@@ -6728,7 +6685,7 @@
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
     </row>
-    <row r="110" spans="1:11" ht="45.75">
+    <row r="110" spans="1:11" ht="43.5">
       <c r="A110" s="21" t="s">
         <v>314</v>
       </c>
@@ -6757,7 +6714,7 @@
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
     </row>
-    <row r="111" spans="1:11" ht="30.75">
+    <row r="111" spans="1:11" ht="29">
       <c r="A111" s="21" t="s">
         <v>26</v>
       </c>
@@ -6786,7 +6743,7 @@
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
     </row>
-    <row r="112" spans="1:11" ht="30.75">
+    <row r="112" spans="1:11" ht="29">
       <c r="A112" s="21" t="s">
         <v>314</v>
       </c>
@@ -6815,7 +6772,7 @@
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
     </row>
-    <row r="113" spans="1:11" ht="30.75">
+    <row r="113" spans="1:11">
       <c r="A113" s="21" t="s">
         <v>314</v>
       </c>
@@ -6844,7 +6801,7 @@
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
     </row>
-    <row r="114" spans="1:11" ht="30.75">
+    <row r="114" spans="1:11" ht="29">
       <c r="A114" s="21" t="s">
         <v>314</v>
       </c>
@@ -6875,7 +6832,7 @@
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
     </row>
-    <row r="115" spans="1:11" ht="30.75">
+    <row r="115" spans="1:11" ht="29">
       <c r="A115" s="21" t="s">
         <v>314</v>
       </c>
@@ -6904,7 +6861,7 @@
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
     </row>
-    <row r="116" spans="1:11" ht="30.75">
+    <row r="116" spans="1:11" ht="29">
       <c r="A116" s="21" t="s">
         <v>314</v>
       </c>
@@ -6933,7 +6890,7 @@
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
     </row>
-    <row r="117" spans="1:11" ht="45.75">
+    <row r="117" spans="1:11" ht="29">
       <c r="A117" s="21" t="s">
         <v>314</v>
       </c>
@@ -6964,7 +6921,7 @@
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
     </row>
-    <row r="118" spans="1:11" ht="45.75">
+    <row r="118" spans="1:11" ht="43.5">
       <c r="A118" s="21" t="s">
         <v>314</v>
       </c>
@@ -6993,7 +6950,7 @@
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
     </row>
-    <row r="119" spans="1:11" ht="30.75">
+    <row r="119" spans="1:11" ht="29">
       <c r="A119" s="21" t="s">
         <v>26</v>
       </c>
@@ -7022,7 +6979,7 @@
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
     </row>
-    <row r="120" spans="1:11" ht="30.75">
+    <row r="120" spans="1:11" ht="29">
       <c r="A120" s="21" t="s">
         <v>314</v>
       </c>
@@ -7051,7 +7008,7 @@
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
     </row>
-    <row r="121" spans="1:11" ht="30.75">
+    <row r="121" spans="1:11" ht="29">
       <c r="A121" s="21" t="s">
         <v>314</v>
       </c>
@@ -7080,7 +7037,7 @@
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
     </row>
-    <row r="122" spans="1:11" ht="30.75">
+    <row r="122" spans="1:11" ht="29">
       <c r="A122" s="21" t="s">
         <v>314</v>
       </c>
@@ -7111,7 +7068,7 @@
       <c r="J122" s="4"/>
       <c r="K122" s="4"/>
     </row>
-    <row r="123" spans="1:11" ht="30.75">
+    <row r="123" spans="1:11" ht="29">
       <c r="A123" s="21" t="s">
         <v>314</v>
       </c>
@@ -7140,7 +7097,7 @@
       <c r="J123" s="4"/>
       <c r="K123" s="4"/>
     </row>
-    <row r="124" spans="1:11" ht="30.75">
+    <row r="124" spans="1:11" ht="29">
       <c r="A124" s="21" t="s">
         <v>314</v>
       </c>
@@ -7169,7 +7126,7 @@
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
     </row>
-    <row r="125" spans="1:11" ht="30.75">
+    <row r="125" spans="1:11" ht="29">
       <c r="A125" s="21" t="s">
         <v>314</v>
       </c>
@@ -7200,7 +7157,7 @@
       <c r="J125" s="4"/>
       <c r="K125" s="4"/>
     </row>
-    <row r="126" spans="1:11" ht="45.75">
+    <row r="126" spans="1:11" ht="43.5">
       <c r="A126" s="21" t="s">
         <v>314</v>
       </c>
@@ -7229,7 +7186,7 @@
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
     </row>
-    <row r="127" spans="1:11" ht="30.75">
+    <row r="127" spans="1:11" ht="29">
       <c r="A127" s="21" t="s">
         <v>314</v>
       </c>
@@ -7258,7 +7215,7 @@
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
     </row>
-    <row r="128" spans="1:11" ht="30.75">
+    <row r="128" spans="1:11" ht="29">
       <c r="A128" s="21" t="s">
         <v>26</v>
       </c>
@@ -7287,7 +7244,7 @@
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
     </row>
-    <row r="129" spans="1:11" ht="30.75">
+    <row r="129" spans="1:11" ht="29">
       <c r="A129" s="21" t="s">
         <v>314</v>
       </c>
@@ -7316,7 +7273,7 @@
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
     </row>
-    <row r="130" spans="1:11" ht="30.75">
+    <row r="130" spans="1:11">
       <c r="A130" s="21" t="s">
         <v>314</v>
       </c>
@@ -7345,7 +7302,7 @@
       <c r="J130" s="4"/>
       <c r="K130" s="4"/>
     </row>
-    <row r="131" spans="1:11" ht="30.75">
+    <row r="131" spans="1:11" ht="29">
       <c r="A131" s="21" t="s">
         <v>314</v>
       </c>
@@ -7376,7 +7333,7 @@
       <c r="J131" s="4"/>
       <c r="K131" s="4"/>
     </row>
-    <row r="132" spans="1:11" ht="30.75">
+    <row r="132" spans="1:11" ht="29">
       <c r="A132" s="21" t="s">
         <v>314</v>
       </c>
@@ -7405,7 +7362,7 @@
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
     </row>
-    <row r="133" spans="1:11" ht="30.75">
+    <row r="133" spans="1:11" ht="29">
       <c r="A133" s="21" t="s">
         <v>314</v>
       </c>
@@ -7434,7 +7391,7 @@
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
     </row>
-    <row r="134" spans="1:11" ht="15">
+    <row r="134" spans="1:11">
       <c r="A134" s="21" t="s">
         <v>314</v>
       </c>
@@ -7463,7 +7420,7 @@
       <c r="J134" s="4"/>
       <c r="K134" s="4"/>
     </row>
-    <row r="135" spans="1:11" ht="45.75">
+    <row r="135" spans="1:11" ht="43.5">
       <c r="A135" s="21" t="s">
         <v>314</v>
       </c>
@@ -7492,7 +7449,7 @@
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
     </row>
-    <row r="136" spans="1:11" ht="30.75">
+    <row r="136" spans="1:11" ht="29">
       <c r="A136" s="21" t="s">
         <v>314</v>
       </c>
@@ -7523,7 +7480,7 @@
       <c r="J136" s="4"/>
       <c r="K136" s="4"/>
     </row>
-    <row r="137" spans="1:11" ht="45.75">
+    <row r="137" spans="1:11" ht="43.5">
       <c r="A137" s="21" t="s">
         <v>314</v>
       </c>
@@ -7552,7 +7509,7 @@
       <c r="J137" s="4"/>
       <c r="K137" s="4"/>
     </row>
-    <row r="138" spans="1:11" ht="30.75">
+    <row r="138" spans="1:11" ht="29">
       <c r="A138" s="21" t="s">
         <v>26</v>
       </c>
@@ -7581,7 +7538,7 @@
       <c r="J138" s="4"/>
       <c r="K138" s="4"/>
     </row>
-    <row r="139" spans="1:11" ht="30.75">
+    <row r="139" spans="1:11" ht="29">
       <c r="A139" s="21" t="s">
         <v>314</v>
       </c>
@@ -7610,7 +7567,7 @@
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
     </row>
-    <row r="140" spans="1:11" ht="15.6" customHeight="1">
+    <row r="140" spans="1:11" ht="15.65" customHeight="1">
       <c r="A140" s="21" t="s">
         <v>314</v>
       </c>
@@ -7639,7 +7596,7 @@
       <c r="J140" s="4"/>
       <c r="K140" s="4"/>
     </row>
-    <row r="141" spans="1:11" ht="30.75">
+    <row r="141" spans="1:11" ht="29">
       <c r="A141" s="21" t="s">
         <v>314</v>
       </c>
@@ -7670,7 +7627,7 @@
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
     </row>
-    <row r="142" spans="1:11" ht="30.75">
+    <row r="142" spans="1:11" ht="29">
       <c r="A142" s="21" t="s">
         <v>314</v>
       </c>
@@ -7699,7 +7656,7 @@
       <c r="J142" s="4"/>
       <c r="K142" s="4"/>
     </row>
-    <row r="143" spans="1:11" ht="137.25">
+    <row r="143" spans="1:11" ht="43.5">
       <c r="A143" s="21" t="s">
         <v>314</v>
       </c>
@@ -7725,22 +7682,18 @@
       <c r="I143" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="J143" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="K143" s="4" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" ht="30.75">
+      <c r="J143" s="4"/>
+      <c r="K143" s="4"/>
+    </row>
+    <row r="144" spans="1:11">
       <c r="A144" s="21" t="s">
         <v>29</v>
       </c>
       <c r="B144" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="C144" s="21" t="s">
         <v>393</v>
-      </c>
-      <c r="C144" s="21" t="s">
-        <v>394</v>
       </c>
       <c r="D144" s="21" t="s">
         <v>310</v>
@@ -7761,7 +7714,7 @@
       <c r="J144" s="4"/>
       <c r="K144" s="4"/>
     </row>
-    <row r="145" spans="1:11" ht="15">
+    <row r="145" spans="1:11">
       <c r="A145" s="21" t="s">
         <v>314</v>
       </c>
@@ -7769,7 +7722,7 @@
         <v>314</v>
       </c>
       <c r="C145" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D145" s="21" t="s">
         <v>314</v>
@@ -7790,7 +7743,7 @@
       <c r="J145" s="4"/>
       <c r="K145" s="4"/>
     </row>
-    <row r="146" spans="1:11" ht="30.75">
+    <row r="146" spans="1:11">
       <c r="A146" s="21" t="s">
         <v>314</v>
       </c>
@@ -7819,7 +7772,7 @@
       <c r="J146" s="4"/>
       <c r="K146" s="4"/>
     </row>
-    <row r="147" spans="1:11" ht="30.75">
+    <row r="147" spans="1:11" ht="29">
       <c r="A147" s="21" t="s">
         <v>314</v>
       </c>
@@ -7850,7 +7803,7 @@
       <c r="J147" s="4"/>
       <c r="K147" s="4"/>
     </row>
-    <row r="148" spans="1:11" ht="30.75">
+    <row r="148" spans="1:11" ht="29">
       <c r="A148" s="21" t="s">
         <v>314</v>
       </c>
@@ -7879,7 +7832,7 @@
       <c r="J148" s="4"/>
       <c r="K148" s="4"/>
     </row>
-    <row r="149" spans="1:11" ht="30.75">
+    <row r="149" spans="1:11" ht="29">
       <c r="A149" s="21" t="s">
         <v>314</v>
       </c>
@@ -7894,13 +7847,13 @@
       </c>
       <c r="E149" s="4"/>
       <c r="F149" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="G149" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="G149" s="21" t="s">
+      <c r="H149" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="H149" s="4" t="s">
-        <v>398</v>
       </c>
       <c r="I149" s="25" t="s">
         <v>80</v>
@@ -7908,7 +7861,7 @@
       <c r="J149" s="4"/>
       <c r="K149" s="4"/>
     </row>
-    <row r="150" spans="1:11" ht="60.75">
+    <row r="150" spans="1:11" ht="43.5">
       <c r="A150" s="21" t="s">
         <v>314</v>
       </c>
@@ -7926,10 +7879,10 @@
         <v>325</v>
       </c>
       <c r="G150" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="H150" s="21" t="s">
         <v>399</v>
-      </c>
-      <c r="H150" s="21" t="s">
-        <v>400</v>
       </c>
       <c r="I150" s="25" t="s">
         <v>80</v>
@@ -7937,18 +7890,18 @@
       <c r="J150" s="4"/>
       <c r="K150" s="4"/>
     </row>
-    <row r="151" spans="1:11" ht="30.75">
+    <row r="151" spans="1:11" ht="29">
       <c r="A151" s="21" t="s">
         <v>29</v>
       </c>
       <c r="B151" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="C151" s="21" t="s">
         <v>401</v>
       </c>
-      <c r="C151" s="21" t="s">
+      <c r="D151" s="21" t="s">
         <v>402</v>
-      </c>
-      <c r="D151" s="21" t="s">
-        <v>403</v>
       </c>
       <c r="E151" s="4"/>
       <c r="F151" s="21" t="s">
@@ -7966,7 +7919,7 @@
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
     </row>
-    <row r="152" spans="1:11" ht="30.75">
+    <row r="152" spans="1:11" ht="29">
       <c r="A152" s="21" t="s">
         <v>314</v>
       </c>
@@ -7974,10 +7927,10 @@
         <v>314</v>
       </c>
       <c r="C152" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="D152" s="21" t="s">
         <v>404</v>
-      </c>
-      <c r="D152" s="21" t="s">
-        <v>405</v>
       </c>
       <c r="E152" s="4"/>
       <c r="F152" s="21" t="s">
@@ -7995,7 +7948,7 @@
       <c r="J152" s="4"/>
       <c r="K152" s="4"/>
     </row>
-    <row r="153" spans="1:11" ht="30.75">
+    <row r="153" spans="1:11">
       <c r="A153" s="21" t="s">
         <v>314</v>
       </c>
@@ -8006,7 +7959,7 @@
         <v>314</v>
       </c>
       <c r="D153" s="21" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E153" s="4"/>
       <c r="F153" s="21" t="s">
@@ -8024,7 +7977,7 @@
       <c r="J153" s="4"/>
       <c r="K153" s="4"/>
     </row>
-    <row r="154" spans="1:11" ht="30.75">
+    <row r="154" spans="1:11" ht="29">
       <c r="A154" s="21" t="s">
         <v>314</v>
       </c>
@@ -8047,7 +8000,7 @@
         <v>319</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I154" s="25" t="s">
         <v>80</v>
@@ -8055,7 +8008,7 @@
       <c r="J154" s="4"/>
       <c r="K154" s="4"/>
     </row>
-    <row r="155" spans="1:11" ht="30.75">
+    <row r="155" spans="1:11" ht="29">
       <c r="A155" s="21" t="s">
         <v>314</v>
       </c>
@@ -8084,7 +8037,7 @@
       <c r="J155" s="4"/>
       <c r="K155" s="4"/>
     </row>
-    <row r="156" spans="1:11" ht="30.75">
+    <row r="156" spans="1:11" ht="29">
       <c r="A156" s="21" t="s">
         <v>314</v>
       </c>
@@ -8099,13 +8052,13 @@
       </c>
       <c r="E156" s="4"/>
       <c r="F156" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G156" s="21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I156" s="25" t="s">
         <v>80</v>
@@ -8113,7 +8066,7 @@
       <c r="J156" s="4"/>
       <c r="K156" s="4"/>
     </row>
-    <row r="157" spans="1:11" ht="76.5">
+    <row r="157" spans="1:11" ht="72.5">
       <c r="A157" s="21" t="s">
         <v>314</v>
       </c>
@@ -8127,16 +8080,16 @@
         <v>314</v>
       </c>
       <c r="E157" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="F157" s="21" t="s">
         <v>409</v>
       </c>
-      <c r="F157" s="21" t="s">
+      <c r="G157" s="21" t="s">
         <v>410</v>
       </c>
-      <c r="G157" s="21" t="s">
+      <c r="H157" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="H157" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="I157" s="25" t="s">
         <v>80</v>
@@ -8144,7 +8097,7 @@
       <c r="J157" s="4"/>
       <c r="K157" s="4"/>
     </row>
-    <row r="158" spans="1:11" ht="60.75">
+    <row r="158" spans="1:11" ht="58">
       <c r="A158" s="21" t="s">
         <v>314</v>
       </c>
@@ -8159,13 +8112,13 @@
       </c>
       <c r="E158" s="4"/>
       <c r="F158" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="G158" s="21" t="s">
         <v>413</v>
       </c>
-      <c r="G158" s="21" t="s">
+      <c r="H158" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="H158" s="4" t="s">
-        <v>415</v>
       </c>
       <c r="I158" s="25" t="s">
         <v>80</v>
@@ -8173,18 +8126,18 @@
       <c r="J158" s="4"/>
       <c r="K158" s="4"/>
     </row>
-    <row r="159" spans="1:11" ht="30.75">
+    <row r="159" spans="1:11" ht="29">
       <c r="A159" s="21" t="s">
         <v>29</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C159" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="D159" s="21" t="s">
         <v>402</v>
-      </c>
-      <c r="D159" s="21" t="s">
-        <v>403</v>
       </c>
       <c r="E159" s="4"/>
       <c r="F159" s="21" t="s">
@@ -8202,7 +8155,7 @@
       <c r="J159" s="4"/>
       <c r="K159" s="4"/>
     </row>
-    <row r="160" spans="1:11" ht="30.75">
+    <row r="160" spans="1:11" ht="29">
       <c r="A160" s="21" t="s">
         <v>314</v>
       </c>
@@ -8210,10 +8163,10 @@
         <v>314</v>
       </c>
       <c r="C160" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="D160" s="21" t="s">
         <v>417</v>
-      </c>
-      <c r="D160" s="21" t="s">
-        <v>418</v>
       </c>
       <c r="E160" s="4"/>
       <c r="F160" s="21" t="s">
@@ -8231,7 +8184,7 @@
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
     </row>
-    <row r="161" spans="1:11" ht="30.75">
+    <row r="161" spans="1:11">
       <c r="A161" s="21" t="s">
         <v>314</v>
       </c>
@@ -8260,7 +8213,7 @@
       <c r="J161" s="4"/>
       <c r="K161" s="4"/>
     </row>
-    <row r="162" spans="1:11" ht="30.75">
+    <row r="162" spans="1:11" ht="29">
       <c r="A162" s="21" t="s">
         <v>314</v>
       </c>
@@ -8283,7 +8236,7 @@
         <v>319</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I162" s="25" t="s">
         <v>80</v>
@@ -8291,7 +8244,7 @@
       <c r="J162" s="4"/>
       <c r="K162" s="4"/>
     </row>
-    <row r="163" spans="1:11" ht="30.75">
+    <row r="163" spans="1:11" ht="29">
       <c r="A163" s="21" t="s">
         <v>314</v>
       </c>
@@ -8320,7 +8273,7 @@
       <c r="J163" s="4"/>
       <c r="K163" s="4"/>
     </row>
-    <row r="164" spans="1:11" ht="30.75">
+    <row r="164" spans="1:11" ht="29">
       <c r="A164" s="21" t="s">
         <v>314</v>
       </c>
@@ -8335,13 +8288,13 @@
       </c>
       <c r="E164" s="4"/>
       <c r="F164" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G164" s="21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I164" s="25" t="s">
         <v>80</v>
@@ -8349,7 +8302,7 @@
       <c r="J164" s="4"/>
       <c r="K164" s="4"/>
     </row>
-    <row r="165" spans="1:11" ht="45.75">
+    <row r="165" spans="1:11" ht="43.5">
       <c r="A165" s="21" t="s">
         <v>314</v>
       </c>
@@ -8363,16 +8316,16 @@
         <v>314</v>
       </c>
       <c r="E165" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="F165" s="21" t="s">
         <v>419</v>
       </c>
-      <c r="F165" s="21" t="s">
+      <c r="G165" s="21" t="s">
         <v>420</v>
       </c>
-      <c r="G165" s="21" t="s">
+      <c r="H165" s="4" t="s">
         <v>421</v>
-      </c>
-      <c r="H165" s="4" t="s">
-        <v>422</v>
       </c>
       <c r="I165" s="25" t="s">
         <v>80</v>
@@ -8380,7 +8333,7 @@
       <c r="J165" s="4"/>
       <c r="K165" s="4"/>
     </row>
-    <row r="166" spans="1:11" ht="45.75">
+    <row r="166" spans="1:11" ht="43.5">
       <c r="A166" s="21" t="s">
         <v>314</v>
       </c>
@@ -8395,13 +8348,13 @@
       </c>
       <c r="E166" s="4"/>
       <c r="F166" s="21" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G166" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="H166" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="H166" s="4" t="s">
-        <v>424</v>
       </c>
       <c r="I166" s="25" t="s">
         <v>80</v>
@@ -8409,18 +8362,18 @@
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
     </row>
-    <row r="167" spans="1:11" ht="30.75">
+    <row r="167" spans="1:11" ht="29">
       <c r="A167" s="21" t="s">
         <v>29</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C167" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="D167" s="21" t="s">
         <v>402</v>
-      </c>
-      <c r="D167" s="21" t="s">
-        <v>403</v>
       </c>
       <c r="E167" s="4"/>
       <c r="F167" s="21" t="s">
@@ -8438,7 +8391,7 @@
       <c r="J167" s="4"/>
       <c r="K167" s="4"/>
     </row>
-    <row r="168" spans="1:11" ht="30.75">
+    <row r="168" spans="1:11" ht="29">
       <c r="A168" s="21" t="s">
         <v>314</v>
       </c>
@@ -8446,10 +8399,10 @@
         <v>314</v>
       </c>
       <c r="C168" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="D168" s="21" t="s">
         <v>426</v>
-      </c>
-      <c r="D168" s="21" t="s">
-        <v>427</v>
       </c>
       <c r="E168" s="4"/>
       <c r="F168" s="21" t="s">
@@ -8467,7 +8420,7 @@
       <c r="J168" s="4"/>
       <c r="K168" s="4"/>
     </row>
-    <row r="169" spans="1:11" ht="30.75">
+    <row r="169" spans="1:11">
       <c r="A169" s="21" t="s">
         <v>314</v>
       </c>
@@ -8478,7 +8431,7 @@
         <v>314</v>
       </c>
       <c r="D169" s="21" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E169" s="4"/>
       <c r="F169" s="21" t="s">
@@ -8496,7 +8449,7 @@
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
     </row>
-    <row r="170" spans="1:11" ht="30.75">
+    <row r="170" spans="1:11" ht="29">
       <c r="A170" s="21" t="s">
         <v>314</v>
       </c>
@@ -8519,7 +8472,7 @@
         <v>319</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I170" s="25" t="s">
         <v>80</v>
@@ -8527,7 +8480,7 @@
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
     </row>
-    <row r="171" spans="1:11" ht="30.75">
+    <row r="171" spans="1:11" ht="29">
       <c r="A171" s="21" t="s">
         <v>314</v>
       </c>
@@ -8556,7 +8509,7 @@
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
     </row>
-    <row r="172" spans="1:11" ht="30.75">
+    <row r="172" spans="1:11" ht="29">
       <c r="A172" s="21" t="s">
         <v>314</v>
       </c>
@@ -8571,13 +8524,13 @@
       </c>
       <c r="E172" s="4"/>
       <c r="F172" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G172" s="21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H172" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I172" s="25" t="s">
         <v>80</v>
@@ -8585,7 +8538,7 @@
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
     </row>
-    <row r="173" spans="1:11" ht="45.75">
+    <row r="173" spans="1:11" ht="43.5">
       <c r="A173" s="21" t="s">
         <v>314</v>
       </c>
@@ -8599,16 +8552,16 @@
         <v>314</v>
       </c>
       <c r="E173" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F173" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="F173" s="21" t="s">
+      <c r="G173" s="21" t="s">
         <v>430</v>
       </c>
-      <c r="G173" s="21" t="s">
+      <c r="H173" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="H173" s="4" t="s">
-        <v>432</v>
       </c>
       <c r="I173" s="25" t="s">
         <v>80</v>
@@ -8616,7 +8569,7 @@
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
     </row>
-    <row r="174" spans="1:11" ht="45.75">
+    <row r="174" spans="1:11" ht="43.5">
       <c r="A174" s="21" t="s">
         <v>314</v>
       </c>
@@ -8631,13 +8584,13 @@
       </c>
       <c r="E174" s="4"/>
       <c r="F174" s="21" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G174" s="21" t="s">
+        <v>432</v>
+      </c>
+      <c r="H174" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="H174" s="4" t="s">
-        <v>434</v>
       </c>
       <c r="I174" s="25" t="s">
         <v>80</v>
@@ -8645,18 +8598,18 @@
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
     </row>
-    <row r="175" spans="1:11" ht="30.75">
+    <row r="175" spans="1:11" ht="29">
       <c r="A175" s="21" t="s">
         <v>29</v>
       </c>
       <c r="B175" s="21" t="s">
+        <v>434</v>
+      </c>
+      <c r="C175" s="21" t="s">
         <v>435</v>
       </c>
-      <c r="C175" s="21" t="s">
-        <v>436</v>
-      </c>
       <c r="D175" s="21" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E175" s="4"/>
       <c r="F175" s="21" t="s">
@@ -8674,7 +8627,7 @@
       <c r="J175" s="4"/>
       <c r="K175" s="4"/>
     </row>
-    <row r="176" spans="1:11" ht="30.75">
+    <row r="176" spans="1:11" ht="29">
       <c r="A176" s="21" t="s">
         <v>314</v>
       </c>
@@ -8682,10 +8635,10 @@
         <v>314</v>
       </c>
       <c r="C176" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="D176" s="21" t="s">
         <v>437</v>
-      </c>
-      <c r="D176" s="21" t="s">
-        <v>438</v>
       </c>
       <c r="E176" s="4"/>
       <c r="F176" s="21" t="s">
@@ -8703,7 +8656,7 @@
       <c r="J176" s="4"/>
       <c r="K176" s="4"/>
     </row>
-    <row r="177" spans="1:11" ht="30.75">
+    <row r="177" spans="1:11">
       <c r="A177" s="21" t="s">
         <v>314</v>
       </c>
@@ -8732,7 +8685,7 @@
       <c r="J177" s="4"/>
       <c r="K177" s="4"/>
     </row>
-    <row r="178" spans="1:11" ht="30.75">
+    <row r="178" spans="1:11" ht="29">
       <c r="A178" s="21" t="s">
         <v>314</v>
       </c>
@@ -8755,7 +8708,7 @@
         <v>319</v>
       </c>
       <c r="H178" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I178" s="4" t="s">
         <v>80</v>
@@ -8763,7 +8716,7 @@
       <c r="J178" s="4"/>
       <c r="K178" s="4"/>
     </row>
-    <row r="179" spans="1:11" ht="30.75">
+    <row r="179" spans="1:11" ht="29">
       <c r="A179" s="21" t="s">
         <v>314</v>
       </c>
@@ -8792,7 +8745,7 @@
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
     </row>
-    <row r="180" spans="1:11" ht="30.75">
+    <row r="180" spans="1:11" ht="29">
       <c r="A180" s="21" t="s">
         <v>314</v>
       </c>
@@ -8807,13 +8760,13 @@
       </c>
       <c r="E180" s="4"/>
       <c r="F180" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G180" s="21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I180" s="4" t="s">
         <v>80</v>
@@ -8821,7 +8774,7 @@
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
     </row>
-    <row r="181" spans="1:11" s="4" customFormat="1" ht="30.75">
+    <row r="181" spans="1:11" s="4" customFormat="1" ht="29">
       <c r="A181" s="21" t="s">
         <v>314</v>
       </c>
@@ -8835,22 +8788,22 @@
         <v>314</v>
       </c>
       <c r="E181" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="F181" s="21" t="s">
         <v>439</v>
-      </c>
-      <c r="F181" s="21" t="s">
-        <v>440</v>
       </c>
       <c r="G181" s="21" t="s">
         <v>337</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I181" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="45.75">
+    <row r="182" spans="1:11" ht="43.5">
       <c r="A182" s="21" t="s">
         <v>314</v>
       </c>
@@ -8868,10 +8821,10 @@
         <v>339</v>
       </c>
       <c r="G182" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="H182" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="H182" s="4" t="s">
-        <v>443</v>
       </c>
       <c r="I182" s="4" t="s">
         <v>80</v>
@@ -8879,18 +8832,18 @@
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
     </row>
-    <row r="183" spans="1:11" s="4" customFormat="1" ht="30.75">
+    <row r="183" spans="1:11" s="4" customFormat="1" ht="29">
       <c r="A183" s="21" t="s">
         <v>29</v>
       </c>
       <c r="B183" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="C183" s="21" t="s">
         <v>444</v>
       </c>
-      <c r="C183" s="21" t="s">
-        <v>445</v>
-      </c>
       <c r="D183" s="21" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F183" s="21" t="s">
         <v>311</v>
@@ -8905,7 +8858,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="15">
+    <row r="184" spans="1:11">
       <c r="A184" s="21" t="s">
         <v>314</v>
       </c>
@@ -8913,10 +8866,10 @@
         <v>314</v>
       </c>
       <c r="C184" s="21" t="s">
+        <v>445</v>
+      </c>
+      <c r="D184" s="21" t="s">
         <v>446</v>
-      </c>
-      <c r="D184" s="21" t="s">
-        <v>447</v>
       </c>
       <c r="E184" s="4"/>
       <c r="F184" s="21" t="s">
@@ -8934,7 +8887,7 @@
       <c r="J184" s="4"/>
       <c r="K184" s="4"/>
     </row>
-    <row r="185" spans="1:11" ht="30.75">
+    <row r="185" spans="1:11">
       <c r="A185" s="21" t="s">
         <v>314</v>
       </c>
@@ -8963,7 +8916,7 @@
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
     </row>
-    <row r="186" spans="1:11" ht="30.75">
+    <row r="186" spans="1:11" ht="29">
       <c r="A186" s="21" t="s">
         <v>314</v>
       </c>
@@ -8986,7 +8939,7 @@
         <v>319</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I186" s="4" t="s">
         <v>80</v>
@@ -8994,7 +8947,7 @@
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
     </row>
-    <row r="187" spans="1:11" ht="30.75">
+    <row r="187" spans="1:11" ht="29">
       <c r="A187" s="21" t="s">
         <v>314</v>
       </c>
@@ -9023,7 +8976,7 @@
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
     </row>
-    <row r="188" spans="1:11" ht="30.75">
+    <row r="188" spans="1:11" ht="29">
       <c r="A188" s="21" t="s">
         <v>314</v>
       </c>
@@ -9038,13 +8991,13 @@
       </c>
       <c r="E188" s="4"/>
       <c r="F188" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G188" s="21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I188" s="4" t="s">
         <v>80</v>
@@ -9052,7 +9005,7 @@
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
     </row>
-    <row r="189" spans="1:11" ht="30.75">
+    <row r="189" spans="1:11" ht="29">
       <c r="A189" s="21" t="s">
         <v>314</v>
       </c>
@@ -9067,13 +9020,13 @@
       </c>
       <c r="E189" s="4"/>
       <c r="F189" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="G189" s="21" t="s">
         <v>448</v>
       </c>
-      <c r="G189" s="21" t="s">
+      <c r="H189" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="H189" s="4" t="s">
-        <v>450</v>
       </c>
       <c r="I189" s="4" t="s">
         <v>80</v>
@@ -9081,18 +9034,18 @@
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
     </row>
-    <row r="190" spans="1:11" ht="30.75">
+    <row r="190" spans="1:11" ht="29">
       <c r="A190" s="21" t="s">
         <v>29</v>
       </c>
       <c r="B190" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="C190" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="C190" s="21" t="s">
-        <v>452</v>
-      </c>
       <c r="D190" s="21" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E190" s="4"/>
       <c r="F190" s="21" t="s">
@@ -9110,7 +9063,7 @@
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
     </row>
-    <row r="191" spans="1:11" ht="30.75">
+    <row r="191" spans="1:11" ht="29">
       <c r="A191" s="21" t="s">
         <v>314</v>
       </c>
@@ -9118,10 +9071,10 @@
         <v>314</v>
       </c>
       <c r="C191" s="21" t="s">
+        <v>452</v>
+      </c>
+      <c r="D191" s="21" t="s">
         <v>453</v>
-      </c>
-      <c r="D191" s="21" t="s">
-        <v>454</v>
       </c>
       <c r="E191" s="4"/>
       <c r="F191" s="21" t="s">
@@ -9139,7 +9092,7 @@
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
     </row>
-    <row r="192" spans="1:11" ht="30.75">
+    <row r="192" spans="1:11">
       <c r="A192" s="21" t="s">
         <v>314</v>
       </c>
@@ -9168,7 +9121,7 @@
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
     </row>
-    <row r="193" spans="1:11" ht="30.75">
+    <row r="193" spans="1:11" ht="29">
       <c r="A193" s="21" t="s">
         <v>314</v>
       </c>
@@ -9191,7 +9144,7 @@
         <v>319</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I193" s="4" t="s">
         <v>80</v>
@@ -9199,7 +9152,7 @@
       <c r="J193" s="4"/>
       <c r="K193" s="4"/>
     </row>
-    <row r="194" spans="1:11" ht="30.75">
+    <row r="194" spans="1:11" ht="29">
       <c r="A194" s="21" t="s">
         <v>314</v>
       </c>
@@ -9228,7 +9181,7 @@
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
     </row>
-    <row r="195" spans="1:11" ht="30.75">
+    <row r="195" spans="1:11" ht="29">
       <c r="A195" s="21" t="s">
         <v>314</v>
       </c>
@@ -9243,13 +9196,13 @@
       </c>
       <c r="E195" s="4"/>
       <c r="F195" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G195" s="21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I195" s="4" t="s">
         <v>80</v>
@@ -9257,7 +9210,7 @@
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
     </row>
-    <row r="196" spans="1:11" ht="30.75">
+    <row r="196" spans="1:11" ht="29">
       <c r="A196" s="21" t="s">
         <v>314</v>
       </c>
@@ -9272,13 +9225,13 @@
       </c>
       <c r="E196" s="4"/>
       <c r="F196" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="G196" s="21" t="s">
         <v>455</v>
       </c>
-      <c r="G196" s="21" t="s">
+      <c r="H196" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="H196" s="4" t="s">
-        <v>457</v>
       </c>
       <c r="I196" s="4" t="s">
         <v>80</v>
@@ -9286,7 +9239,7 @@
       <c r="J196" s="4"/>
       <c r="K196" s="4"/>
     </row>
-    <row r="197" spans="1:11" ht="30.75">
+    <row r="197" spans="1:11" ht="29">
       <c r="A197" s="21" t="s">
         <v>314</v>
       </c>
@@ -9301,13 +9254,13 @@
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="G197" s="21" t="s">
         <v>458</v>
       </c>
-      <c r="G197" s="21" t="s">
+      <c r="H197" s="4" t="s">
         <v>459</v>
-      </c>
-      <c r="H197" s="4" t="s">
-        <v>460</v>
       </c>
       <c r="I197" s="4" t="s">
         <v>80</v>
@@ -9315,7 +9268,7 @@
       <c r="J197" s="4"/>
       <c r="K197" s="4"/>
     </row>
-    <row r="198" spans="1:11" ht="30.75">
+    <row r="198" spans="1:11" ht="29">
       <c r="A198" s="21" t="s">
         <v>314</v>
       </c>
@@ -9330,13 +9283,13 @@
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="G198" s="21" t="s">
         <v>461</v>
       </c>
-      <c r="G198" s="21" t="s">
+      <c r="H198" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="H198" s="4" t="s">
-        <v>463</v>
       </c>
       <c r="I198" s="4" t="s">
         <v>80</v>
@@ -9344,7 +9297,7 @@
       <c r="J198" s="4"/>
       <c r="K198" s="4"/>
     </row>
-    <row r="199" spans="1:11" ht="30.75">
+    <row r="199" spans="1:11" ht="29">
       <c r="A199" s="21" t="s">
         <v>314</v>
       </c>
@@ -9359,13 +9312,13 @@
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="G199" s="21" t="s">
         <v>464</v>
       </c>
-      <c r="G199" s="21" t="s">
+      <c r="H199" s="4" t="s">
         <v>465</v>
-      </c>
-      <c r="H199" s="4" t="s">
-        <v>466</v>
       </c>
       <c r="I199" s="4" t="s">
         <v>80</v>
@@ -9373,18 +9326,18 @@
       <c r="J199" s="4"/>
       <c r="K199" s="4"/>
     </row>
-    <row r="200" spans="1:11" ht="30.75">
+    <row r="200" spans="1:11" ht="29">
       <c r="A200" s="21" t="s">
         <v>29</v>
       </c>
       <c r="B200" s="21" t="s">
+        <v>466</v>
+      </c>
+      <c r="C200" s="21" t="s">
         <v>467</v>
       </c>
-      <c r="C200" s="21" t="s">
-        <v>468</v>
-      </c>
       <c r="D200" s="21" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="21" t="s">
@@ -9402,7 +9355,7 @@
       <c r="J200" s="4"/>
       <c r="K200" s="4"/>
     </row>
-    <row r="201" spans="1:11" ht="15">
+    <row r="201" spans="1:11">
       <c r="A201" s="21" t="s">
         <v>314</v>
       </c>
@@ -9413,7 +9366,7 @@
         <v>344</v>
       </c>
       <c r="D201" s="21" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E201" s="4"/>
       <c r="F201" s="21" t="s">
@@ -9431,7 +9384,7 @@
       <c r="J201" s="4"/>
       <c r="K201" s="4"/>
     </row>
-    <row r="202" spans="1:11" ht="30.75">
+    <row r="202" spans="1:11">
       <c r="A202" s="21" t="s">
         <v>314</v>
       </c>
@@ -9460,7 +9413,7 @@
       <c r="J202" s="4"/>
       <c r="K202" s="4"/>
     </row>
-    <row r="203" spans="1:11" ht="30.75">
+    <row r="203" spans="1:11" ht="29">
       <c r="A203" s="21" t="s">
         <v>314</v>
       </c>
@@ -9483,7 +9436,7 @@
         <v>319</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I203" s="4" t="s">
         <v>80</v>
@@ -9491,7 +9444,7 @@
       <c r="J203" s="4"/>
       <c r="K203" s="4"/>
     </row>
-    <row r="204" spans="1:11" ht="30.75">
+    <row r="204" spans="1:11" ht="29">
       <c r="A204" s="21" t="s">
         <v>314</v>
       </c>
@@ -9520,7 +9473,7 @@
       <c r="J204" s="4"/>
       <c r="K204" s="4"/>
     </row>
-    <row r="205" spans="1:11" ht="30.75">
+    <row r="205" spans="1:11" ht="29">
       <c r="A205" s="21" t="s">
         <v>314</v>
       </c>
@@ -9535,13 +9488,13 @@
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G205" s="21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H205" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I205" s="4" t="s">
         <v>80</v>
@@ -9549,7 +9502,7 @@
       <c r="J205" s="4"/>
       <c r="K205" s="4"/>
     </row>
-    <row r="206" spans="1:11" ht="30.75">
+    <row r="206" spans="1:11" ht="29">
       <c r="A206" s="21" t="s">
         <v>314</v>
       </c>
@@ -9563,16 +9516,16 @@
         <v>314</v>
       </c>
       <c r="E206" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="F206" s="21" t="s">
         <v>470</v>
       </c>
-      <c r="F206" s="21" t="s">
+      <c r="G206" s="21" t="s">
         <v>471</v>
       </c>
-      <c r="G206" s="21" t="s">
+      <c r="H206" s="4" t="s">
         <v>472</v>
-      </c>
-      <c r="H206" s="4" t="s">
-        <v>473</v>
       </c>
       <c r="I206" s="4" t="s">
         <v>80</v>
@@ -9580,7 +9533,7 @@
       <c r="J206" s="4"/>
       <c r="K206" s="4"/>
     </row>
-    <row r="207" spans="1:11" ht="229.5">
+    <row r="207" spans="1:11" ht="203">
       <c r="A207" s="21" t="s">
         <v>314</v>
       </c>
@@ -9595,36 +9548,36 @@
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="G207" s="21" t="s">
         <v>474</v>
       </c>
-      <c r="G207" s="21" t="s">
+      <c r="H207" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="H207" s="4" t="s">
-        <v>476</v>
       </c>
       <c r="I207" s="4" t="s">
         <v>152</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>477</v>
+        <v>391</v>
       </c>
       <c r="K207" s="4" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="208" spans="1:11" ht="30.75">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" ht="29">
       <c r="A208" s="21" t="s">
         <v>29</v>
       </c>
       <c r="B208" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C208" s="21" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D208" s="21" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="21" t="s">
@@ -9642,7 +9595,7 @@
       <c r="J208" s="4"/>
       <c r="K208" s="4"/>
     </row>
-    <row r="209" spans="1:11" ht="15">
+    <row r="209" spans="1:11">
       <c r="A209" s="21" t="s">
         <v>314</v>
       </c>
@@ -9650,10 +9603,10 @@
         <v>314</v>
       </c>
       <c r="C209" s="21" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D209" s="21" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="21" t="s">
@@ -9671,7 +9624,7 @@
       <c r="J209" s="4"/>
       <c r="K209" s="4"/>
     </row>
-    <row r="210" spans="1:11" ht="30.75">
+    <row r="210" spans="1:11">
       <c r="A210" s="21" t="s">
         <v>314</v>
       </c>
@@ -9700,7 +9653,7 @@
       <c r="J210" s="4"/>
       <c r="K210" s="4"/>
     </row>
-    <row r="211" spans="1:11" ht="30.75">
+    <row r="211" spans="1:11" ht="29">
       <c r="A211" s="21" t="s">
         <v>314</v>
       </c>
@@ -9723,7 +9676,7 @@
         <v>319</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I211" s="4" t="s">
         <v>80</v>
@@ -9731,7 +9684,7 @@
       <c r="J211" s="4"/>
       <c r="K211" s="4"/>
     </row>
-    <row r="212" spans="1:11" ht="30.75">
+    <row r="212" spans="1:11" ht="29">
       <c r="A212" s="21" t="s">
         <v>314</v>
       </c>
@@ -9760,7 +9713,7 @@
       <c r="J212" s="4"/>
       <c r="K212" s="4"/>
     </row>
-    <row r="213" spans="1:11" ht="30.75">
+    <row r="213" spans="1:11" ht="29">
       <c r="A213" s="21" t="s">
         <v>314</v>
       </c>
@@ -9775,13 +9728,13 @@
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="G213" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="G213" s="21" t="s">
+      <c r="H213" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="H213" s="4" t="s">
-        <v>398</v>
       </c>
       <c r="I213" s="4" t="s">
         <v>80</v>
@@ -9789,7 +9742,7 @@
       <c r="J213" s="4"/>
       <c r="K213" s="4"/>
     </row>
-    <row r="214" spans="1:11" ht="167.25">
+    <row r="214" spans="1:11" ht="29">
       <c r="A214" s="21" t="s">
         <v>314</v>
       </c>
@@ -9804,692 +9757,688 @@
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="G214" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="H214" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="G214" s="21" t="s">
-        <v>484</v>
-      </c>
-      <c r="H214" s="4" t="s">
-        <v>485</v>
       </c>
       <c r="I214" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="J214" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="K214" s="4" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="215" spans="1:11" ht="45.75">
+      <c r="J214" s="4"/>
+      <c r="K214" s="4"/>
+    </row>
+    <row r="215" spans="1:11" ht="29">
       <c r="A215" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E215" s="4"/>
       <c r="F215" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="I215" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J215" s="4"/>
       <c r="K215" s="4"/>
     </row>
-    <row r="216" spans="1:11" ht="30.75">
+    <row r="216" spans="1:11">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
       <c r="F216" s="4" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="G216" s="4" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="I216" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J216" s="4"/>
       <c r="K216" s="4"/>
     </row>
-    <row r="217" spans="1:11" ht="183">
+    <row r="217" spans="1:11" ht="174">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
       <c r="F217" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G217" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="H217" s="4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="I217" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J217" s="4"/>
       <c r="K217" s="4"/>
     </row>
-    <row r="218" spans="1:11" ht="45.75">
+    <row r="218" spans="1:11" ht="29">
       <c r="A218" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="G218" s="4" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="I218" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J218" s="4"/>
       <c r="K218" s="4"/>
     </row>
-    <row r="219" spans="1:11" ht="30.75">
+    <row r="219" spans="1:11" ht="29">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
       <c r="F219" s="4" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G219" s="4" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="I219" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J219" s="4"/>
       <c r="K219" s="4"/>
     </row>
-    <row r="220" spans="1:11" ht="30.75">
+    <row r="220" spans="1:11" ht="29">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
       <c r="F220" s="4" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G220" s="4" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="H220" s="4" t="s">
         <v>89</v>
       </c>
       <c r="I220" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
     </row>
-    <row r="221" spans="1:11" ht="76.5">
+    <row r="221" spans="1:11" ht="72.5">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
       <c r="F221" s="4" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="I221" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J221" s="4"/>
       <c r="K221" s="4"/>
     </row>
-    <row r="222" spans="1:11" ht="45.75">
+    <row r="222" spans="1:11" ht="29">
       <c r="A222" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="G222" s="4" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="I222" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J222" s="4"/>
       <c r="K222" s="4"/>
     </row>
-    <row r="223" spans="1:11" ht="30.75">
+    <row r="223" spans="1:11" ht="29">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
       <c r="F223" s="4" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I223" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J223" s="4"/>
       <c r="K223" s="4"/>
     </row>
-    <row r="224" spans="1:11" ht="91.5">
+    <row r="224" spans="1:11" ht="87">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
       <c r="F224" s="4" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G224" s="4" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="I224" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J224" s="4"/>
       <c r="K224" s="4"/>
     </row>
-    <row r="225" spans="1:11" ht="45.75">
+    <row r="225" spans="1:11" ht="29">
       <c r="A225" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E225" s="4"/>
       <c r="F225" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="I225" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J225" s="4"/>
       <c r="K225" s="4"/>
     </row>
-    <row r="226" spans="1:11" ht="30.75">
+    <row r="226" spans="1:11" ht="29">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="G226" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="H226" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="I226" s="4" t="s">
         <v>523</v>
-      </c>
-      <c r="F226" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="G226" s="4" t="s">
-        <v>525</v>
-      </c>
-      <c r="H226" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="I226" s="4" t="s">
-        <v>527</v>
       </c>
       <c r="J226" s="4"/>
       <c r="K226" s="4"/>
     </row>
-    <row r="227" spans="1:11" ht="15">
+    <row r="227" spans="1:11">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
       <c r="F227" s="4" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="I227" s="4" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="J227" s="4"/>
       <c r="K227" s="4"/>
     </row>
-    <row r="228" spans="1:11" ht="45.75">
+    <row r="228" spans="1:11" ht="29">
       <c r="A228" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="G228" s="4" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="I228" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J228" s="4"/>
       <c r="K228" s="4"/>
     </row>
-    <row r="229" spans="1:11" ht="30.75">
+    <row r="229" spans="1:11" ht="29">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
       <c r="F229" s="4" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="H229" s="4" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="I229" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J229" s="4"/>
       <c r="K229" s="4"/>
     </row>
-    <row r="230" spans="1:11" ht="30.75">
+    <row r="230" spans="1:11" ht="29">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
       <c r="F230" s="4" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="I230" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J230" s="4"/>
       <c r="K230" s="4"/>
     </row>
-    <row r="231" spans="1:11" ht="30.75">
+    <row r="231" spans="1:11" ht="29">
       <c r="A231" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E231" s="4"/>
       <c r="F231" s="4" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="I231" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J231" s="4"/>
       <c r="K231" s="4"/>
     </row>
-    <row r="232" spans="1:11" ht="15">
+    <row r="232" spans="1:11">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
       <c r="F232" s="4" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="G232" s="4" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="I232" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J232" s="4"/>
       <c r="K232" s="4"/>
     </row>
-    <row r="233" spans="1:11" ht="137.25">
+    <row r="233" spans="1:11" ht="130.5">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
       <c r="F233" s="4" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="I233" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J233" s="4"/>
       <c r="K233" s="4"/>
     </row>
-    <row r="234" spans="1:11" ht="60.75">
+    <row r="234" spans="1:11" ht="58">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
       <c r="F234" s="4" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="I234" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
     </row>
-    <row r="235" spans="1:11" ht="30.75">
+    <row r="235" spans="1:11" ht="29">
       <c r="A235" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E235" s="4"/>
       <c r="F235" s="4" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="H235" s="4" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="I235" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J235" s="4"/>
       <c r="K235" s="4"/>
     </row>
-    <row r="236" spans="1:11" ht="30.75">
+    <row r="236" spans="1:11" ht="29">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
       <c r="F236" s="4" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G236" s="4" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I236" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J236" s="4"/>
       <c r="K236" s="4"/>
     </row>
-    <row r="237" spans="1:11" ht="15">
+    <row r="237" spans="1:11">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
       <c r="F237" s="4" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="I237" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J237" s="4"/>
       <c r="K237" s="4"/>
     </row>
-    <row r="238" spans="1:11" ht="15">
+    <row r="238" spans="1:11">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
       <c r="F238" s="4" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="G238" s="4" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="I238" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J238" s="4"/>
       <c r="K238" s="4"/>
     </row>
-    <row r="239" spans="1:11" ht="30.75">
+    <row r="239" spans="1:11" ht="29">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
       <c r="F239" s="4" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="I239" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J239" s="4"/>
       <c r="K239" s="4"/>
     </row>
-    <row r="240" spans="1:11" ht="15">
+    <row r="240" spans="1:11">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
       <c r="F240" s="4" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="G240" s="4" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="I240" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J240" s="4"/>
       <c r="K240" s="4"/>
     </row>
-    <row r="241" spans="1:11" ht="15">
+    <row r="241" spans="1:11">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
       <c r="F241" s="4" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="I241" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J241" s="4"/>
       <c r="K241" s="4"/>
     </row>
-    <row r="242" spans="1:11" ht="45.75">
+    <row r="242" spans="1:11" ht="43.5">
       <c r="A242" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="E242" s="4"/>
       <c r="F242" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="G242" s="4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="H242" s="4"/>
       <c r="I242" s="4"/>
       <c r="J242" s="4"/>
       <c r="K242" s="4"/>
     </row>
-    <row r="243" spans="1:11" ht="30.75">
+    <row r="243" spans="1:11" ht="29">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
       <c r="F243" s="4" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="H243" s="4"/>
       <c r="I243" s="4"/>
       <c r="J243" s="4"/>
       <c r="K243" s="4"/>
     </row>
-    <row r="244" spans="1:11" ht="229.5">
+    <row r="244" spans="1:11" ht="217.5">
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -10498,169 +10447,169 @@
       </c>
       <c r="E244" s="4"/>
       <c r="F244" s="4" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="G244" s="4" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="H244" s="4"/>
       <c r="I244" s="4"/>
       <c r="J244" s="4"/>
       <c r="K244" s="4"/>
     </row>
-    <row r="245" spans="1:11" ht="45.75">
+    <row r="245" spans="1:11" ht="43.5">
       <c r="A245" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="E245" s="4"/>
       <c r="F245" s="4" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
       <c r="J245" s="4"/>
       <c r="K245" s="4"/>
     </row>
-    <row r="246" spans="1:11" ht="15">
+    <row r="246" spans="1:11">
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
       <c r="F246" s="4" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="G246" s="4" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="H246" s="4"/>
       <c r="I246" s="4"/>
       <c r="J246" s="4"/>
       <c r="K246" s="4"/>
     </row>
-    <row r="247" spans="1:11" ht="30.75">
+    <row r="247" spans="1:11" ht="29">
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
       <c r="F247" s="4" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
       <c r="J247" s="4"/>
       <c r="K247" s="4"/>
     </row>
-    <row r="248" spans="1:11" ht="30.75">
+    <row r="248" spans="1:11" ht="29">
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
       <c r="F248" s="4" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="G248" s="4" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="H248" s="4"/>
       <c r="I248" s="4"/>
       <c r="J248" s="4"/>
       <c r="K248" s="4"/>
     </row>
-    <row r="249" spans="1:11" ht="15">
+    <row r="249" spans="1:11">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
       <c r="F249" s="4" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="H249" s="4"/>
       <c r="I249" s="4"/>
       <c r="J249" s="4"/>
       <c r="K249" s="4"/>
     </row>
-    <row r="250" spans="1:11" ht="45.75">
+    <row r="250" spans="1:11" ht="43.5">
       <c r="A250" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="E250" s="4"/>
       <c r="F250" s="4" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G250" s="4" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="H250" s="4"/>
       <c r="I250" s="4"/>
       <c r="J250" s="4"/>
       <c r="K250" s="4"/>
     </row>
-    <row r="251" spans="1:11" ht="76.5">
+    <row r="251" spans="1:11" ht="72.5">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
       <c r="F251" s="4" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="H251" s="4"/>
       <c r="I251" s="4"/>
       <c r="J251" s="4"/>
       <c r="K251" s="4"/>
     </row>
-    <row r="252" spans="1:11" ht="15">
+    <row r="252" spans="1:11">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
       <c r="F252" s="4" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G252" s="4" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
       <c r="J252" s="4"/>
       <c r="K252" s="4"/>
     </row>
-    <row r="253" spans="1:11" ht="30.75">
+    <row r="253" spans="1:11" ht="29">
       <c r="A253" s="4"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -10668,56 +10617,56 @@
       <c r="E253" s="4"/>
       <c r="F253" s="4"/>
       <c r="G253" s="4" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="H253" s="4"/>
       <c r="I253" s="4"/>
       <c r="J253" s="4"/>
       <c r="K253" s="4"/>
     </row>
-    <row r="254" spans="1:11" s="4" customFormat="1" ht="30.75">
+    <row r="254" spans="1:11" s="4" customFormat="1" ht="29">
       <c r="A254" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B254" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="E254" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="F254" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="C254" s="4" t="s">
+      <c r="G254" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="D254" s="4" t="s">
+      <c r="H254" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="E254" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="F254" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="G254" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="H254" s="4" t="s">
-        <v>600</v>
-      </c>
       <c r="I254" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="30.75">
+    <row r="255" spans="1:11" ht="29">
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
       <c r="F255" s="4" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="I255" s="4" t="s">
         <v>80</v>
@@ -10725,26 +10674,26 @@
       <c r="J255" s="4"/>
       <c r="K255" s="4"/>
     </row>
-    <row r="256" spans="1:11" ht="30.75">
+    <row r="256" spans="1:11" ht="29">
       <c r="A256" s="4"/>
       <c r="B256" s="4" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E256" s="4"/>
       <c r="F256" s="4" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="G256" s="4" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="I256" s="4" t="s">
         <v>80</v>
@@ -10752,20 +10701,20 @@
       <c r="J256" s="4"/>
       <c r="K256" s="4"/>
     </row>
-    <row r="257" spans="1:11" ht="30.75">
+    <row r="257" spans="1:11" ht="29">
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
       <c r="F257" s="4" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="H257" s="4" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="I257" s="4" t="s">
         <v>80</v>
@@ -10773,20 +10722,20 @@
       <c r="J257" s="4"/>
       <c r="K257" s="4"/>
     </row>
-    <row r="258" spans="1:11" ht="30.75">
+    <row r="258" spans="1:11" ht="29">
       <c r="A258" s="4"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
       <c r="F258" s="4" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="H258" s="4" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="I258" s="4" t="s">
         <v>80</v>
@@ -10794,26 +10743,26 @@
       <c r="J258" s="4"/>
       <c r="K258" s="4"/>
     </row>
-    <row r="259" spans="1:11" ht="30.75">
+    <row r="259" spans="1:11" ht="29">
       <c r="A259" s="4"/>
       <c r="B259" s="4" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="E259" s="4"/>
       <c r="F259" s="4" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H259" s="4" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="I259" s="4" t="s">
         <v>80</v>
@@ -10821,20 +10770,20 @@
       <c r="J259" s="4"/>
       <c r="K259" s="4"/>
     </row>
-    <row r="260" spans="1:11" ht="30.75">
+    <row r="260" spans="1:11" ht="29">
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
       <c r="F260" s="4" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="H260" s="4" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="I260" s="4" t="s">
         <v>80</v>
@@ -10842,26 +10791,26 @@
       <c r="J260" s="4"/>
       <c r="K260" s="4"/>
     </row>
-    <row r="261" spans="1:11" ht="45.75">
+    <row r="261" spans="1:11" ht="43.5">
       <c r="A261" s="4"/>
       <c r="B261" s="4" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="E261" s="4"/>
       <c r="F261" s="4" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="I261" s="4" t="s">
         <v>80</v>
@@ -10869,28 +10818,28 @@
       <c r="J261" s="4"/>
       <c r="K261" s="4"/>
     </row>
-    <row r="262" spans="1:11" ht="30.75">
+    <row r="262" spans="1:11" ht="29">
       <c r="A262" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E262" s="4"/>
       <c r="F262" s="4" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="G262" s="4" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="I262" s="4" t="s">
         <v>80</v>
@@ -10898,20 +10847,20 @@
       <c r="J262" s="4"/>
       <c r="K262" s="4"/>
     </row>
-    <row r="263" spans="1:11" ht="30.75">
+    <row r="263" spans="1:11" ht="29">
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
       <c r="F263" s="4" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="I263" s="4" t="s">
         <v>80</v>
@@ -10919,20 +10868,20 @@
       <c r="J263" s="4"/>
       <c r="K263" s="4"/>
     </row>
-    <row r="264" spans="1:11" ht="30.75">
+    <row r="264" spans="1:11" ht="29">
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
       <c r="F264" s="4" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="G264" s="4" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="I264" s="4" t="s">
         <v>80</v>
@@ -10940,26 +10889,26 @@
       <c r="J264" s="4"/>
       <c r="K264" s="4"/>
     </row>
-    <row r="265" spans="1:11" ht="30.75">
+    <row r="265" spans="1:11" ht="29">
       <c r="A265" s="4"/>
       <c r="B265" s="4" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="E265" s="4"/>
       <c r="F265" s="4" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="I265" s="4" t="s">
         <v>80</v>
@@ -10967,20 +10916,20 @@
       <c r="J265" s="4"/>
       <c r="K265" s="4"/>
     </row>
-    <row r="266" spans="1:11" ht="30.75">
+    <row r="266" spans="1:11" ht="29">
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
       <c r="F266" s="4" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="G266" s="4" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I266" s="4" t="s">
         <v>80</v>
@@ -10988,20 +10937,20 @@
       <c r="J266" s="4"/>
       <c r="K266" s="4"/>
     </row>
-    <row r="267" spans="1:11" ht="30.75">
+    <row r="267" spans="1:11" ht="29">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
       <c r="F267" s="4" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="I267" s="4" t="s">
         <v>80</v>
@@ -11009,20 +10958,20 @@
       <c r="J267" s="4"/>
       <c r="K267" s="4"/>
     </row>
-    <row r="268" spans="1:11" ht="30.75">
+    <row r="268" spans="1:11" ht="29">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
       <c r="F268" s="4" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="I268" s="4" t="s">
         <v>80</v>
@@ -11030,26 +10979,26 @@
       <c r="J268" s="4"/>
       <c r="K268" s="4"/>
     </row>
-    <row r="269" spans="1:11" ht="30.75">
+    <row r="269" spans="1:11" ht="29">
       <c r="A269" s="4"/>
       <c r="B269" s="26" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="E269" s="4"/>
       <c r="F269" s="4" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="G269" s="4" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="H269" s="4" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="I269" s="4" t="s">
         <v>80</v>
@@ -11057,20 +11006,20 @@
       <c r="J269" s="4"/>
       <c r="K269" s="4"/>
     </row>
-    <row r="270" spans="1:11" ht="30.75">
+    <row r="270" spans="1:11" ht="29">
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
       <c r="F270" s="4" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="G270" s="4" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H270" s="4" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="I270" s="4" t="s">
         <v>80</v>
@@ -11078,20 +11027,20 @@
       <c r="J270" s="4"/>
       <c r="K270" s="4"/>
     </row>
-    <row r="271" spans="1:11" ht="30.75">
+    <row r="271" spans="1:11" ht="29">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
       <c r="F271" s="4" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="G271" s="4" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="H271" s="4" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="I271" s="4" t="s">
         <v>80</v>
@@ -11099,20 +11048,20 @@
       <c r="J271" s="4"/>
       <c r="K271" s="4"/>
     </row>
-    <row r="272" spans="1:11" ht="30.75">
+    <row r="272" spans="1:11" ht="29">
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
       <c r="F272" s="4" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="G272" s="4" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="H272" s="4" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="I272" s="4" t="s">
         <v>80</v>
@@ -11125,23 +11074,23 @@
         <v>47</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="D273" s="10" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="E273" s="10"/>
       <c r="F273" s="4" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="G273" s="4" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="H273" s="4" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="I273" s="4" t="s">
         <v>80</v>
@@ -11156,13 +11105,13 @@
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
       <c r="F274" s="4" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="G274" s="10" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="H274" s="4" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="I274" s="4" t="s">
         <v>80</v>
@@ -11177,13 +11126,13 @@
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
       <c r="F275" s="4" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="G275" s="10" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="H275" s="4" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="I275" s="4" t="s">
         <v>80</v>
@@ -11191,26 +11140,26 @@
       <c r="J275" s="4"/>
       <c r="K275" s="4"/>
     </row>
-    <row r="276" spans="1:11" ht="30.75">
+    <row r="276" spans="1:11" ht="29">
       <c r="A276" s="4"/>
       <c r="B276" s="4" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E276" s="4"/>
       <c r="F276" s="4" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="G276" s="4" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H276" s="4" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="I276" s="4" t="s">
         <v>80</v>
@@ -11218,20 +11167,20 @@
       <c r="J276" s="4"/>
       <c r="K276" s="4"/>
     </row>
-    <row r="277" spans="1:11" ht="30.75">
+    <row r="277" spans="1:11" ht="29">
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
       <c r="D277" s="4"/>
       <c r="E277" s="4"/>
       <c r="F277" s="4" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="H277" s="4" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="I277" s="4" t="s">
         <v>80</v>
@@ -11239,26 +11188,26 @@
       <c r="J277" s="4"/>
       <c r="K277" s="4"/>
     </row>
-    <row r="278" spans="1:11" ht="30.75">
+    <row r="278" spans="1:11" ht="29">
       <c r="A278" s="4"/>
       <c r="B278" s="4" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="E278" s="4"/>
       <c r="F278" s="4" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="G278" s="4" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="H278" s="4" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="I278" s="4" t="s">
         <v>80</v>
@@ -11266,20 +11215,20 @@
       <c r="J278" s="4"/>
       <c r="K278" s="4"/>
     </row>
-    <row r="279" spans="1:11" ht="45.75">
+    <row r="279" spans="1:11" ht="43.5">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
       <c r="F279" s="4" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="G279" s="4" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="H279" s="4" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="I279" s="4" t="s">
         <v>80</v>
@@ -11287,20 +11236,20 @@
       <c r="J279" s="4"/>
       <c r="K279" s="4"/>
     </row>
-    <row r="280" spans="1:11" ht="15">
+    <row r="280" spans="1:11">
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
       <c r="F280" s="4" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="G280" s="4" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="H280" s="4" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="I280" s="4" t="s">
         <v>80</v>
@@ -11308,26 +11257,26 @@
       <c r="J280" s="4"/>
       <c r="K280" s="4"/>
     </row>
-    <row r="281" spans="1:11" ht="30.75">
+    <row r="281" spans="1:11" ht="29">
       <c r="A281" s="4"/>
       <c r="B281" s="4" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="E281" s="4"/>
       <c r="F281" s="4" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="G281" s="4" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="H281" s="27" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="I281" s="4" t="s">
         <v>80</v>
@@ -11335,20 +11284,20 @@
       <c r="J281" s="4"/>
       <c r="K281" s="4"/>
     </row>
-    <row r="282" spans="1:11" ht="15">
+    <row r="282" spans="1:11">
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
       <c r="D282" s="4"/>
       <c r="E282" s="4"/>
       <c r="F282" s="4" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="G282" s="4" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="H282" s="4" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="I282" s="4" t="s">
         <v>80</v>
@@ -11356,20 +11305,20 @@
       <c r="J282" s="4"/>
       <c r="K282" s="4"/>
     </row>
-    <row r="283" spans="1:11" ht="30.75">
+    <row r="283" spans="1:11" ht="29">
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
       <c r="F283" s="4" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="G283" s="4" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="H283" s="4" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="I283" s="4" t="s">
         <v>80</v>
@@ -11382,89 +11331,89 @@
         <v>51</v>
       </c>
       <c r="B287" s="11" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C287" s="11" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="D287" s="11" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="E287" s="11"/>
       <c r="F287" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G287" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="I287" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="288" spans="1:11">
       <c r="F288" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G288" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="I288" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="F289" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G289" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I289" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="F290" s="12" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="G290" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I290" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="291" spans="1:9">
       <c r="F291" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G291" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="I291" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="292" spans="1:9">
       <c r="F292" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="G292" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="I292" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="293" spans="1:9">
       <c r="F293" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="G293" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="I293" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="294" spans="1:9">
@@ -11472,88 +11421,88 @@
         <v>51</v>
       </c>
       <c r="B294" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C294" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="D294" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="F294" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G294" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="I294" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="295" spans="1:9">
       <c r="F295" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G295" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="I295" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="296" spans="1:9">
       <c r="F296" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G296" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I296" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="297" spans="1:9">
       <c r="F297" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="G297" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I297" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="298" spans="1:9">
       <c r="F298" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G298" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="I298" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="F299" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="G299" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="I299" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="F300" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="G300" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="I300" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="301" spans="1:9">
@@ -11561,99 +11510,99 @@
         <v>51</v>
       </c>
       <c r="B301" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="C301" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="D301" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="F301" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G301" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="I301" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="302" spans="1:9">
       <c r="F302" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G302" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="I302" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="303" spans="1:9">
       <c r="F303" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G303" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I303" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="304" spans="1:9">
       <c r="F304" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="G304" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I304" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="F305" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G305" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="I305" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="306" spans="1:9">
       <c r="F306" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G306" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="I306" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="307" spans="1:9">
       <c r="F307" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="G307" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="I307" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="308" spans="1:9">
       <c r="F308" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G308" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="I308" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="309" spans="1:9">
@@ -11661,88 +11610,88 @@
         <v>51</v>
       </c>
       <c r="B309" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="C309" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="D309" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="F309" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G309" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="I309" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="310" spans="1:9">
       <c r="F310" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G310" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="I310" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="311" spans="1:9">
       <c r="F311" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G311" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I311" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="312" spans="1:9">
       <c r="F312" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="G312" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I312" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="313" spans="1:9">
       <c r="F313" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G313" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="I313" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="314" spans="1:9">
       <c r="F314" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="G314" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="I314" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="315" spans="1:9">
       <c r="F315" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="G315" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="I315" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -11750,110 +11699,110 @@
         <v>55</v>
       </c>
       <c r="B316" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="C316" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="D316" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="F316" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G316" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="I316" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="F317" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G317" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="I317" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="F318" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G318" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I318" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="319" spans="1:9">
       <c r="F319" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="G319" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I319" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="F320" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G320" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="I320" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="F321" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="G321" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="I321" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="F322" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="G322" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="I322" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="F323" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="G323" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="I323" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="F324" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="G324" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="I324" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="325" spans="1:9">
@@ -11861,99 +11810,99 @@
         <v>55</v>
       </c>
       <c r="B325" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="C325" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="D325" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="F325" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G325" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="I325" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="326" spans="1:9">
       <c r="F326" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G326" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="I326" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="327" spans="1:9">
       <c r="F327" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G327" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I327" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="328" spans="1:9">
       <c r="F328" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="G328" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I328" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="329" spans="1:9">
       <c r="F329" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G329" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="I329" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="330" spans="1:9">
       <c r="F330" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="G330" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="I330" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="331" spans="1:9">
       <c r="F331" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="G331" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="I331" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="332" spans="1:9">
       <c r="F332" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="G332" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="I332" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -11966,30 +11915,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA580A90-ED50-48A5-A305-F0EC915677BC}">
   <dimension ref="A1:K67"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="44.5703125" customWidth="1"/>
-    <col min="3" max="3" width="78.85546875" customWidth="1"/>
-    <col min="4" max="4" width="62.42578125" customWidth="1"/>
-    <col min="5" max="5" width="84.85546875" customWidth="1"/>
-    <col min="6" max="6" width="59.42578125" customWidth="1"/>
-    <col min="7" max="7" width="60.42578125" customWidth="1"/>
-    <col min="8" max="8" width="79.42578125" customWidth="1"/>
-    <col min="10" max="10" width="62.42578125" customWidth="1"/>
+    <col min="2" max="2" width="44.54296875" customWidth="1"/>
+    <col min="3" max="3" width="78.81640625" customWidth="1"/>
+    <col min="4" max="4" width="62.453125" customWidth="1"/>
+    <col min="5" max="5" width="84.81640625" customWidth="1"/>
+    <col min="6" max="6" width="59.453125" customWidth="1"/>
+    <col min="7" max="7" width="60.453125" customWidth="1"/>
+    <col min="8" max="8" width="79.453125" customWidth="1"/>
+    <col min="10" max="10" width="62.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="F1" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="H1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -12029,37 +11978,37 @@
     </row>
     <row r="11" spans="1:11">
       <c r="I11" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="I12" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="I13" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="I14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="I15" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="I16" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="I17" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -12067,99 +12016,99 @@
         <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="C18" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="D18" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="F18" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G18" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="I18" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="F19" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G19" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="I19" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="F20" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G20" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I20" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="F21" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="G21" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I21" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="F22" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G22" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="I22" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="F23" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G23" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="I23" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="F24" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="G24" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="I24" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="F25" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G25" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="I25" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -12167,88 +12116,88 @@
         <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="C26" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="D26" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="F26" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G26" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="I26" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="F27" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G27" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="I27" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="F28" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G28" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I28" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="F29" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="G29" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I29" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="F30" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G30" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="I30" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="F31" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="G31" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="I31" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="F32" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="G32" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="I32" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -12256,110 +12205,110 @@
         <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="C33" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="D33" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="F33" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G33" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="I33" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="F34" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G34" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="I34" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="F35" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G35" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I35" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="F36" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="G36" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I36" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="F37" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G37" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="I37" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="F38" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="G38" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="I38" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="F39" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="G39" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="I39" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="F40" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="G40" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="I40" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="F41" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="G41" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="I41" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -12367,99 +12316,99 @@
         <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="C42" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="D42" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="F42" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G42" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="I42" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="F43" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G43" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="I43" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="F44" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G44" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I44" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="F45" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="G45" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I45" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="F46" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G46" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="I46" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="F47" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="G47" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="I47" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="F48" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="G48" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="I48" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="F49" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="G49" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="I49" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -12467,26 +12416,26 @@
         <v>51</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="E52" s="17"/>
       <c r="F52" s="18" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="H52" s="18" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="I52" s="18" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -12495,19 +12444,19 @@
       <c r="C53" s="18"/>
       <c r="D53" s="18"/>
       <c r="E53" s="19" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="F53" s="18" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="H53" s="18" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="I53" s="18" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -12517,16 +12466,16 @@
       <c r="D54" s="18"/>
       <c r="E54" s="18"/>
       <c r="F54" s="18" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G54" s="18" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="H54" s="18" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="I54" s="18" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -12536,16 +12485,16 @@
       <c r="D55" s="18"/>
       <c r="E55" s="18"/>
       <c r="F55" s="18" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="I55" s="18" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -12554,19 +12503,19 @@
       <c r="C56" s="18"/>
       <c r="D56" s="18"/>
       <c r="E56" s="18" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="F56" s="18" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="I56" s="18" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -12575,19 +12524,19 @@
       <c r="C57" s="18"/>
       <c r="D57" s="18"/>
       <c r="E57" s="18" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="H57" s="18" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="I57" s="18" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -12597,16 +12546,16 @@
       <c r="D58" s="18"/>
       <c r="E58" s="18"/>
       <c r="F58" s="18" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G58" s="18" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="H58" s="18" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="I58" s="18" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -12616,16 +12565,16 @@
       <c r="D59" s="18"/>
       <c r="E59" s="18"/>
       <c r="F59" s="18" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="I59" s="18" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -12635,16 +12584,16 @@
       <c r="D60" s="18"/>
       <c r="E60" s="18"/>
       <c r="F60" s="18" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="I60" s="18" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -12652,20 +12601,20 @@
         <v>377</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="E61" s="18"/>
       <c r="F61" s="18" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="H61" s="18"/>
       <c r="I61" s="18"/>
@@ -12677,10 +12626,10 @@
       <c r="D62" s="18"/>
       <c r="E62" s="18"/>
       <c r="F62" s="18" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G62" s="18" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -12690,10 +12639,10 @@
       <c r="D63" s="18"/>
       <c r="E63" s="18"/>
       <c r="F63" s="18" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -12703,10 +12652,10 @@
       <c r="D64" s="18"/>
       <c r="E64" s="18"/>
       <c r="F64" s="18" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -12716,10 +12665,10 @@
       <c r="D65" s="18"/>
       <c r="E65" s="18"/>
       <c r="F65" s="18" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -12729,10 +12678,10 @@
       <c r="D66" s="18"/>
       <c r="E66" s="18"/>
       <c r="F66" s="18" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -12742,10 +12691,10 @@
       <c r="D67" s="18"/>
       <c r="E67" s="18"/>
       <c r="F67" s="18" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="G67" s="18" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -12759,57 +12708,57 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.26953125" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="42.7265625" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="40.85546875" customWidth="1"/>
+    <col min="5" max="5" width="40.81640625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.1796875" customWidth="1"/>
+    <col min="8" max="8" width="19.1796875" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" customWidth="1"/>
+    <col min="10" max="10" width="18.26953125" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="15">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>786</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>790</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="213">
+    <row r="2" spans="1:11" ht="203">
       <c r="A2">
         <v>1</v>
       </c>
@@ -12817,31 +12766,31 @@
         <v>153</v>
       </c>
       <c r="C2" t="s">
+        <v>787</v>
+      </c>
+      <c r="D2" t="s">
+        <v>788</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="F2" t="s">
+        <v>790</v>
+      </c>
+      <c r="G2" t="s">
+        <v>790</v>
+      </c>
+      <c r="H2" t="s">
         <v>791</v>
-      </c>
-      <c r="D2" t="s">
-        <v>792</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>793</v>
-      </c>
-      <c r="F2" t="s">
-        <v>794</v>
-      </c>
-      <c r="G2" t="s">
-        <v>794</v>
-      </c>
-      <c r="H2" t="s">
-        <v>795</v>
       </c>
       <c r="I2" s="16">
         <v>46199</v>
       </c>
       <c r="J2" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="244.5">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="232">
       <c r="A3">
         <v>2</v>
       </c>
@@ -12849,31 +12798,31 @@
         <v>241</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D3" t="s">
+        <v>788</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="F3" t="s">
+        <v>795</v>
+      </c>
+      <c r="G3" t="s">
+        <v>796</v>
+      </c>
+      <c r="H3" t="s">
         <v>797</v>
-      </c>
-      <c r="D3" t="s">
-        <v>792</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>798</v>
-      </c>
-      <c r="F3" t="s">
-        <v>799</v>
-      </c>
-      <c r="G3" t="s">
-        <v>800</v>
-      </c>
-      <c r="H3" t="s">
-        <v>801</v>
       </c>
       <c r="I3" s="16">
         <v>46199</v>
       </c>
       <c r="J3" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="244.5">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="232">
       <c r="A4">
         <v>3</v>
       </c>
@@ -12881,31 +12830,31 @@
         <v>247</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="D4" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="F4" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="G4" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="H4" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="I4" s="16">
         <v>46199</v>
       </c>
       <c r="J4" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="244.5">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="232">
       <c r="A5">
         <v>4</v>
       </c>
@@ -12913,31 +12862,31 @@
         <v>252</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="D5" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F5" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="G5" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="H5" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="I5" s="16">
         <v>46199</v>
       </c>
       <c r="J5" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="259.5">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="246.5">
       <c r="A6">
         <v>5</v>
       </c>
@@ -12945,31 +12894,31 @@
         <v>271</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="D6" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="F6" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="G6" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="H6" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="I6" s="16">
         <v>46199</v>
       </c>
       <c r="J6" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="336">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="304.5">
       <c r="A7">
         <v>6</v>
       </c>
@@ -12977,134 +12926,90 @@
         <v>282</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="D7" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="F7" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="G7" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="H7" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="I7" s="16">
         <v>46199</v>
       </c>
       <c r="J7" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="305.25">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="290">
       <c r="A8" s="22" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B8" s="21" t="s">
         <v>391</v>
       </c>
       <c r="C8" s="21" t="s">
+        <v>809</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>788</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>810</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>795</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>796</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>807</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>808</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>792</v>
+      </c>
+      <c r="K8" s="21" t="s">
         <v>811</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>792</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>812</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>799</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>800</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>813</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>814</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>796</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="305.25">
-      <c r="A9" s="22" t="s">
-        <v>815</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>477</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>816</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>792</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>817</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>799</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>800</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>813</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>814</v>
-      </c>
-      <c r="J9" s="21" t="s">
-        <v>796</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="336">
-      <c r="A10" s="22" t="s">
-        <v>819</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>486</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>820</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>792</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>821</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>799</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>800</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>813</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>814</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>796</v>
-      </c>
-      <c r="K10" s="21" t="s">
-        <v>822</v>
-      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="22"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="22"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13115,36 +13020,36 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="29.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.7265625" customWidth="1"/>
+    <col min="5" max="5" width="29.1796875" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="15">
+    <row r="1" spans="1:6" s="2" customFormat="1">
       <c r="A1" s="23" t="s">
-        <v>823</v>
+        <v>812</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>824</v>
+        <v>813</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>825</v>
+        <v>814</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>826</v>
+        <v>815</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>63</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="30.75">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="29">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -13152,17 +13057,17 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>828</v>
+        <v>817</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6" ht="15">
+    <row r="3" spans="1:6">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -13170,19 +13075,19 @@
         <v>2.1</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>830</v>
+        <v>819</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>831</v>
+        <v>820</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>832</v>
+        <v>821</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15">
+    <row r="4" spans="1:6">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -13198,7 +13103,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" ht="15">
+    <row r="5" spans="1:6">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -13206,7 +13111,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>833</v>
+        <v>822</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>23</v>
@@ -13214,7 +13119,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" ht="15">
+    <row r="6" spans="1:6">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -13222,15 +13127,17 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>834</v>
+        <v>823</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>835</v>
+      </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" ht="15">
+    <row r="7" spans="1:6" ht="29">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -13238,15 +13145,19 @@
         <v>6.1</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>835</v>
+        <v>824</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" ht="15">
+      <c r="E7" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -13262,7 +13173,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="15">
+    <row r="9" spans="1:6">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -13278,7 +13189,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" ht="15">
+    <row r="10" spans="1:6">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -13286,7 +13197,7 @@
         <v>9.1</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>836</v>
+        <v>825</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>39</v>
@@ -13294,7 +13205,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" ht="15">
+    <row r="11" spans="1:6">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -13302,19 +13213,19 @@
         <v>10.1</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>837</v>
+        <v>826</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>838</v>
+        <v>827</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -13322,19 +13233,19 @@
         <v>11.1</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -13342,19 +13253,19 @@
         <v>12.1</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>47</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>843</v>
+        <v>832</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -13362,7 +13273,7 @@
         <v>13.1</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>51</v>
@@ -13370,7 +13281,7 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" ht="15">
+    <row r="15" spans="1:6">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -13378,7 +13289,7 @@
         <v>14.1</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>55</v>
